--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -845,7 +711,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1259,7 +1125,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1455,7 +1321,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-11-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1501,7 +1367,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-10-18</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1547,7 +1413,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-02-20</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1593,7 +1459,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1823,7 +1689,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1869,7 +1735,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1915,7 +1781,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2195,7 +2061,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-10-31</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2241,7 +2107,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2287,7 +2153,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-09</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2333,7 +2199,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-10-06</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2379,7 +2245,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2475,7 +2341,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2521,7 +2387,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3219,7 +3085,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3365,7 +3231,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3411,7 +3277,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3457,7 +3323,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3503,7 +3369,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3599,7 +3465,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3745,7 +3611,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3791,7 +3657,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3887,7 +3753,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3933,7 +3799,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-10-04</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3979,7 +3845,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-11</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4025,7 +3891,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-18</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4255,7 +4121,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-10</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4301,7 +4167,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4347,7 +4213,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4995,7 +4861,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-02-15</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5187,7 +5053,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5279,7 +5145,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5325,7 +5191,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5559,7 +5425,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-07</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5605,7 +5471,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-06-16</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5651,7 +5517,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-17</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5697,7 +5563,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5743,7 +5609,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-23</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5789,7 +5655,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-09-28</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5835,7 +5701,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-03-25</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5881,7 +5747,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-30</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5927,7 +5793,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5973,7 +5839,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6019,7 +5885,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-20</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6065,7 +5931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6111,7 +5977,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-02-18</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6157,7 +6023,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6203,7 +6069,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-02-28</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6249,7 +6115,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6295,7 +6161,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6341,7 +6207,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6387,7 +6253,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-03-21</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6433,7 +6299,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6479,7 +6345,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-30</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6617,7 +6483,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-07</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6663,7 +6529,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-11-17</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6709,7 +6575,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6755,7 +6621,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2007-08-23</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6801,7 +6667,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2006-08-16</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6847,7 +6713,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2007-06-28</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6989,7 +6855,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2007-08-22</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7085,7 +6951,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7131,7 +6997,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-05-18</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7177,7 +7043,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-12-27</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7223,7 +7089,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-01-06</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7269,7 +7135,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-03-20</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7365,7 +7231,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7411,7 +7277,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7657,7 +7523,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7703,7 +7569,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2017-07-31</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7749,7 +7615,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-06-27</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7795,7 +7661,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-06-27</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7841,7 +7707,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2017-07-30</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7887,7 +7753,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7933,7 +7799,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7979,7 +7845,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-04-12</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -8025,7 +7891,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8071,7 +7937,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-11-11</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8117,7 +7983,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8163,7 +8029,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-18</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8209,7 +8075,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2010-12-30</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8255,7 +8121,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-11-08</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8347,7 +8213,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-12</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8393,7 +8259,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8439,7 +8305,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-23</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8485,7 +8351,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-09-29</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8531,7 +8397,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-21</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8577,7 +8443,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-23</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8623,7 +8489,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8819,7 +8685,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8865,7 +8731,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2008-03-26</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8911,7 +8777,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-05-29</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8957,7 +8823,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -9003,7 +8869,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-06-01</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -9049,7 +8915,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9095,7 +8961,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-16</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9141,7 +9007,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9187,7 +9053,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-04-19</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9283,7 +9149,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-16</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9329,7 +9195,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-23</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9375,7 +9241,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-06-13</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9421,7 +9287,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-03-08</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9467,7 +9333,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-18</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9513,7 +9379,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9559,7 +9425,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-11-05</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9605,7 +9471,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-18</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9651,7 +9517,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-06</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9697,7 +9563,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-16</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9743,7 +9609,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-03-16</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9789,7 +9655,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-23</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9885,7 +9751,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9931,7 +9797,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9977,7 +9843,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-13</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -10023,7 +9889,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-17</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10069,7 +9935,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10115,7 +9981,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-11-12</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10161,7 +10027,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-30</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10207,7 +10073,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-16</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10253,7 +10119,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10299,7 +10165,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10395,7 +10261,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10441,7 +10307,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10487,7 +10353,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10583,7 +10449,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2010-12-30</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10629,7 +10495,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10675,7 +10541,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-31</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10721,7 +10587,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-10</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10767,7 +10633,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-13</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10813,7 +10679,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10859,7 +10725,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-23</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10905,7 +10771,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-11</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10951,7 +10817,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2010-12-28</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10997,7 +10863,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -11043,7 +10909,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11089,7 +10955,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2010-12-19</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11135,7 +11001,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2010-12-19</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11181,7 +11047,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11227,7 +11093,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-07</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11273,7 +11139,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11319,7 +11185,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-05</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11365,7 +11231,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11461,7 +11327,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-20</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11507,7 +11373,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11553,7 +11419,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-03-15</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11599,7 +11465,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11645,7 +11511,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11691,7 +11557,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11737,7 +11603,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11783,7 +11649,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11829,7 +11695,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11875,7 +11741,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11921,7 +11787,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11967,7 +11833,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -12013,7 +11879,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-07</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -12059,7 +11925,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12105,7 +11971,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12151,7 +12017,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12197,7 +12063,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-27</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12243,7 +12109,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-27</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12289,7 +12155,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-27</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12335,7 +12201,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-16</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12381,7 +12247,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12427,7 +12293,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12473,7 +12339,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12519,7 +12385,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12565,7 +12431,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12611,7 +12477,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12657,7 +12523,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12703,7 +12569,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12749,7 +12615,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12795,7 +12661,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-30</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12841,7 +12707,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -12887,7 +12753,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12933,7 +12799,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -12955,2835 +12821,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>罗便臣道80号 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>130 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>112 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2059呎 (3房)
-$8,888万
-$43,167/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 2093呎 (3房)
-$10,528万
-$50,301/呎
-(17年-01月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 1437呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 1709呎 (3房)
-$6,300万
-$36,864/呎
-(16年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1058呎 (3房)
-$52,262万
-$493,971/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52,262万
-$488,431/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52,262万
-$611,253/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$52,262万
-$611,253/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1083呎 (3房)
-$52,262万
-$482,568/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 879呎 (3房)
-$52,262万
-$594,563/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$52,262万
-$611,253/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1083呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,550万
-$29,825/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3,467万
-$32,956/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3,130万
-$29,252/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,866万
-$33,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,643万
-$30,917/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52,262万
-$488,431/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52,262万
-$611,253/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$52,262万
-$611,253/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3,250万
-$30,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,830万
-$33,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,620万
-$30,643/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$52,262万
-$488,431/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$52,262万
-$611,253/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 879呎 (3房)
-$52,262万
-$594,563/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3,426万
-$32,564/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1083呎 (3房)
-$2,950万
-$27,239/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,833万
-$33,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,640万
-$30,871/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3,100万
-$29,468/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1070呎 (3房)
-$3,418万
-$31,944/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,430万
-$28,421/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1064呎 (3房)
-$52,262万
-$491,185/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 865呎 (3房)
-$52,262万
-$604,186/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$1,269万
-$12,064/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$3,030万
-$29,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$1,255万
-$11,931/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,550万
-$30,321/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$1,305万
-$12,405/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$1,008万
-$11,994/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2,750万
-$26,141/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 865呎 (3房)
-$2,370万
-$27,399/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$2,280万
-$22,093/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1065呎 (3房)
-$2,553万
-$23,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,578万
-$30,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$2,339万
-$27,842/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52,262万
-$622,168/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2,800万
-$26,616/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,350万
-$27,943/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$889万
-$10,585/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52,262万
-$622,168/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1064呎 (3房)
-$52,262万
-$491,185/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 865呎 (3房)
-$52,262万
-$604,186/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52,262万
-$622,168/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$52,262万
-$496,788/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52,262万
-$622,168/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$52,262万
-$506,416/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$894万
-$10,637/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-$998万
-$9,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$2,680万
-$25,720/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,370万
-$28,181/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$843万
-$10,032/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 1032呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1056呎 (3房)
-$52,262万
-$494,906/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$52,262万
-$621,428/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$52,262万
-$622,168/呎
-(04年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (2房)
-$550万
-$8,863/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$2,088万
-$20,038/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$1,960万
-$23,306/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$760万
-$9,048/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 618呎 (2房)
-$465万
-$7,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$1,049万
-$10,067/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,083万
-$24,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$1,670万
-$19,881/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 618呎 (2房)
-$482万
-$7,799/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$2,188万
-$20,998/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$881万
-$10,476/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$785万
-$9,345/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 618呎 (2房)
-$529万
-$8,560/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$2,210万
-$21,209/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,034万
-$24,186/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$690万
-$8,211/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>13/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 618呎 (2房)
-$520万
-$8,414/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 1056呎 (3房)
-$2,158万
-$20,438/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,040万
-$24,257/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$730万
-$8,692/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 618呎 (2房)
-$433万
-$7,010/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$52,262万
-$501,556/呎
-(04年-11月)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$4,719万
-$56,108/呎
-(15年-12月)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$662万
-$7,883/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr"/>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$2,561万
-$24,579/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$1,911万
-$22,717/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>罗便臣道80号 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>134 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>119 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 2010呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1995呎 (3房)
-$4,300万
-$21,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 1366呎 (3房)
-$2,963万
-$21,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 1366呎 (3房)
-$3,330万
-$24,378/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2181呎 (3房)
-$7,618万
-$34,928/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 2158呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 1412呎 (3房)
-$2,980万
-$21,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 1412呎 (3房)
-$6,110万
-$43,275/呎
-(15年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-$2,900万
-$27,103/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$3,442万
-$32,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,798万
-$32,722/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,410万
-$28,187/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$3,300万
-$31,369/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,590万
-$30,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-$1,363万
-$12,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-$3,860万
-$36,075/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2,789万
-$26,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,511万
-$29,371/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,850万
-$33,333/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-$2,925万
-$27,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2,663万
-$25,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,700万
-$31,579/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,630万
-$30,760/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-$2,650万
-$24,766/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2,580万
-$24,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,685万
-$31,399/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,619万
-$30,628/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1083呎 (3房)
-$1,288万
-$11,893/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$2,520万
-$23,954/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$4,719万
-$55,189/呎
-(15年-12月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,602万
-$30,436/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-$2,715万
-$25,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-$3,372万
-$32,055/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-$2,685万
-$31,399/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$2,265万
-$26,491/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1070呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 855呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 855呎 (3房)
-$988万
-$11,557/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$3,376万
-$32,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$2,448万
-$23,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$1,792万
-$21,307/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$2,560万
-$30,440/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$1,192万
-$11,335/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$2,250万
-$21,802/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,080万
-$24,732/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$2,154万
-$25,612/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1065呎 (3房)
-$2,350万
-$22,066/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$2,210万
-$21,415/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 865呎 (3房)
-$920万
-$10,631/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$1,167万
-$11,093/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$2,160万
-$20,930/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 841呎 (3房)
-$2,083万
-$24,768/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$2,118万
-$25,184/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$1,210万
-$11,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1038呎 (3房)
-$2,160万
-$20,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$1,960万
-$23,333/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$2,380万
-$28,299/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$1,197万
-$11,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$1,990万
-$23,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$2,000万
-$23,781/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1064呎 (3房)
-$1,125万
-$10,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$2,100万
-$20,349/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$1,900万
-$22,619/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$946万
-$11,253/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$1,140万
-$10,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1038呎 (3房)
-$2,140万
-$20,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$1,990万
-$23,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$2,363万
-$28,103/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$1,015万
-$9,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$953万
-$9,232/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$946万
-$11,249/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1052呎 (3房)
-$1,064万
-$10,113/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$1,950万
-$18,895/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$896万
-$10,649/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1064呎 (3房)
-$1,061万
-$9,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$1,938万
-$18,779/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 863呎 (2房)
-$1,810万
-$20,973/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$1,838万
-$21,855/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1064呎 (3房)
-$1,040万
-$9,773/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$1,900万
-$18,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$1,740万
-$20,714/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$1,790万
-$21,284/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1065呎 (3房)
-$942万
-$8,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$1,867万
-$18,094/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 865呎 (2房)
-$1,723万
-$19,916/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$913万
-$10,856/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$1,065万
-$10,221/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$1,918万
-$18,585/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$881万
-$10,492/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-$733万
-$8,721/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$1,015万
-$9,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1039呎 (3房)
-$892万
-$8,586/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$1,780万
-$21,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 841呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1056呎 (3房)
-$832万
-$7,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1032呎 (3房)
-$840万
-$8,140/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$750万
-$8,935/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 865呎 (3房)
-$769万
-$8,890/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$858万
-$8,234/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 618呎 (2房)
-$487万
-$7,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$791万
-$9,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (2房)
-$733万
-$8,717/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$891万
-$8,548/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 619呎 (2房)
-$486万
-$7,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$723万
-$8,607/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 841呎 (2房)
-$715万
-$8,501/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$828万
-$7,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 618呎 (2房)
-$481万
-$7,783/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$709万
-$8,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 865呎 (2房)
-$754万
-$8,716/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$866万
-$8,311/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 618呎 (2房)
-$426万
-$6,893/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$650万
-$7,736/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$1,490万
-$17,738/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>13/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 1056呎 (3房)
-$855万
-$8,097/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 618呎 (2房)
-$456万
-$7,385/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$724万
-$8,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$718万
-$8,548/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$760万
-$7,295/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 618呎 (2房)
-$373万
-$6,042/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>C | 840呎 (2房)
-$707万
-$8,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$667万
-$7,936/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 1042呎 (3房)
-$732万
-$7,022/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr"/>
-      <c r="D39" s="18" t="inlineStr"/>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 840呎 (2房)
-$662万
-$7,875/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +137,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +218,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -12821,4 +12992,2835 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2059呎 (3房)
+$8888万
+$43,167/呎
+(16年-09月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 2093呎 (3房)
+$10528万
+$50,301/呎
+(17年-01月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 1437呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 1709呎 (3房)
+$6300万
+$36,864/呎
+(16年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (3房)
+$52262万
+$493,971/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$52262万
+$488,431/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$52262万
+$482,568/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2550万
+$29,825/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$3467万
+$32,956/呎
+(16年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$3130万
+$29,252/呎
+(11年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2866万
+$33,518/呎
+(15年-10月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2643万
+$30,917/呎
+(15年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$52262万
+$488,431/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$3250万
+$30,374/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2830万
+$33,099/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2620万
+$30,643/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$52262万
+$488,431/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$52262万
+$611,253/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 879呎 (3房)
+$52262万
+$594,563/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$3426万
+$32,564/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+$2950万
+$27,239/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2833万
+$33,133/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2640万
+$30,871/呎
+(16年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$3100万
+$29,468/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1070呎 (3房)
+$3418万
+$31,944/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2430万
+$28,421/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$1269万
+$12,064/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$3030万
+$29,360/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$1255万
+$11,931/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2550万
+$30,321/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$1305万
+$12,405/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$1008万
+$11,994/呎
+(01年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$2750万
+$26,141/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$2370万
+$27,399/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$2280万
+$22,093/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1065呎 (3房)
+$2553万
+$23,972/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2578万
+$30,649/呎
+(15年-10月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$2339万
+$27,842/呎
+(16年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$2800万
+$26,616/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2350万
+$27,943/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$889万
+$10,585/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1064呎 (3房)
+$52262万
+$491,185/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (3房)
+$52262万
+$604,186/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$52262万
+$496,788/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$52262万
+$506,416/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$894万
+$10,637/呎
+(02年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+$998万
+$9,671/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$2680万
+$25,720/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2370万
+$28,181/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$843万
+$10,032/呎
+(01年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1032呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1056呎 (3房)
+$52262万
+$494,906/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$52262万
+$621,428/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$52262万
+$622,168/呎
+(04年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (2房)
+$550万
+$8,863/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$2088万
+$20,038/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$1960万
+$23,306/呎
+(11年-06月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$760万
+$9,048/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 618呎 (2房)
+$465万
+$7,518/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$1049万
+$10,067/呎
+(02年-03月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2083万
+$24,774/呎
+(15年-09月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$1670万
+$19,881/呎
+(11年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 618呎 (2房)
+$482万
+$7,799/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$2188万
+$20,998/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$881万
+$10,476/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$785万
+$9,345/呎
+(01年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 618呎 (2房)
+$529万
+$8,560/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$2210万
+$21,209/呎
+(11年-02月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2034万
+$24,186/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$690万
+$8,211/呎
+(02年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 618呎 (2房)
+$520万
+$8,414/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 1056呎 (3房)
+$2158万
+$20,438/呎
+(11年-03月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2040万
+$24,257/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$730万
+$8,692/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 618呎 (2房)
+$433万
+$7,010/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$52262万
+$501,556/呎
+(04年-11月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$4719万
+$56,108/呎
+(15年-12月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$662万
+$7,883/呎
+(01年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr"/>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$2561万
+$24,579/呎
+(15年-11月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$1911万
+$22,717/呎
+(15年-11月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 2010呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1995呎 (3房)
+$4300万
+$21,554/呎
+(07年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1366呎 (3房)
+$2963万
+$21,690/呎
+(06年-08月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 1366呎 (3房)
+$3330万
+$24,378/呎
+(07年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2181呎 (3房)
+$7618万
+$34,928/呎
+(16年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2158呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1412呎 (3房)
+$2980万
+$21,105/呎
+(07年-08月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 1412呎 (3房)
+$6110万
+$43,275/呎
+(15年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+$2900万
+$27,103/呎
+(11年-03月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$3442万
+$32,721/呎
+(16年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2798万
+$32,722/呎
+(15年-12月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2410万
+$28,187/呎
+(11年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$3300万
+$31,369/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2590万
+$30,292/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+$1363万
+$12,738/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+$3860万
+$36,075/呎
+(17年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$2789万
+$26,510/呎
+(11年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2511万
+$29,371/呎
+(11年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2850万
+$33,333/呎
+(17年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+$2925万
+$27,336/呎
+(11年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$2663万
+$25,312/呎
+(11年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2700万
+$31,579/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2630万
+$30,760/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+$2650万
+$24,766/呎
+(10年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$2580万
+$24,525/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2685万
+$31,399/呎
+(15年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2619万
+$30,628/呎
+(15年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1083呎 (3房)
+$1288万
+$11,893/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$2520万
+$23,954/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$4719万
+$55,189/呎
+(15年-12月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2602万
+$30,436/呎
+(15年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+$2715万
+$25,374/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+$3372万
+$32,055/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+$2685万
+$31,399/呎
+(15年-09月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$2265万
+$26,491/呎
+(11年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1070呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 855呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 855呎 (3房)
+$988万
+$11,557/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$3376万
+$32,095/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$2448万
+$23,721/呎
+(11年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$1792万
+$21,307/呎
+(08年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$2560万
+$30,440/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$1192万
+$11,335/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$2250万
+$21,802/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2080万
+$24,732/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$2154万
+$25,612/呎
+(11年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1065呎 (3房)
+$2350万
+$22,066/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$2210万
+$21,415/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (3房)
+$920万
+$10,631/呎
+(02年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$1167万
+$11,093/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$2160万
+$20,930/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 841呎 (3房)
+$2083万
+$24,768/呎
+(11年-03月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$2118万
+$25,184/呎
+(11年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$1210万
+$11,507/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1038呎 (3房)
+$2160万
+$20,809/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$1960万
+$23,333/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$2380万
+$28,299/呎
+(15年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$1197万
+$11,378/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$1990万
+$23,690/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$2000万
+$23,781/呎
+(11年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1064呎 (3房)
+$1125万
+$10,573/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$2100万
+$20,349/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$1900万
+$22,619/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$946万
+$11,253/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$1140万
+$10,833/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1038呎 (3房)
+$2140万
+$20,617/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$1990万
+$23,690/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$2363万
+$28,103/呎
+(15年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$1015万
+$9,651/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$953万
+$9,232/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$946万
+$11,249/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (3房)
+$1064万
+$10,113/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$1950万
+$18,895/呎
+(10年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$896万
+$10,649/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1064呎 (3房)
+$1061万
+$9,976/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$1938万
+$18,779/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 863呎 (2房)
+$1810万
+$20,973/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$1838万
+$21,855/呎
+(11年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1064呎 (3房)
+$1040万
+$9,773/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$1900万
+$18,411/呎
+(10年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$1740万
+$20,714/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$1790万
+$21,284/呎
+(11年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1065呎 (3房)
+$942万
+$8,848/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$1867万
+$18,094/呎
+(10年-12月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 865呎 (2房)
+$1723万
+$19,916/呎
+(10年-12月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$913万
+$10,856/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$1065万
+$10,221/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$1918万
+$18,585/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$881万
+$10,492/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+$733万
+$8,721/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$1015万
+$9,740/呎
+(02年-03月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1039呎 (3房)
+$892万
+$8,586/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$1780万
+$21,190/呎
+(11年-01月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 841呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1056呎 (3房)
+$832万
+$7,877/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1032呎 (3房)
+$840万
+$8,140/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$750万
+$8,935/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (3房)
+$769万
+$8,890/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$858万
+$8,234/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 618呎 (2房)
+$487万
+$7,880/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$791万
+$9,417/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (2房)
+$733万
+$8,717/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$891万
+$8,548/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 619呎 (2房)
+$486万
+$7,851/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$723万
+$8,607/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 841呎 (2房)
+$715万
+$8,501/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$828万
+$7,947/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 618呎 (2房)
+$481万
+$7,783/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$709万
+$8,445/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 865呎 (2房)
+$754万
+$8,716/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$866万
+$8,311/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 618呎 (2房)
+$426万
+$6,893/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$650万
+$7,736/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$1490万
+$17,738/呎
+(11年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 1056呎 (3房)
+$855万
+$8,097/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 618呎 (2房)
+$456万
+$7,385/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$724万
+$8,625/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$718万
+$8,548/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$760万
+$7,295/呎
+(02年-01月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 618呎 (2房)
+$373万
+$6,042/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 840呎 (2房)
+$707万
+$8,417/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$667万
+$7,936/呎
+(01年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 1042呎 (3房)
+$732万
+$7,022/呎
+(01年-12月)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr"/>
+      <c r="D38" s="22" t="inlineStr"/>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 840呎 (2房)
+$662万
+$7,875/呎
+(02年-01月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -645,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J266"/>
+  <dimension ref="A1:N266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -648,6 +648,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -705,6 +709,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -751,6 +775,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -801,6 +845,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -847,6 +911,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -893,6 +977,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -939,6 +1043,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -985,6 +1109,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1031,6 +1175,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1077,6 +1241,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1123,6 +1307,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1169,6 +1373,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1215,6 +1439,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1261,6 +1505,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1307,6 +1571,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1357,6 +1641,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1407,6 +1711,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1457,6 +1781,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1503,6 +1847,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1549,6 +1913,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1595,6 +1979,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1641,6 +2045,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1687,6 +2111,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1733,6 +2177,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1779,6 +2243,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1825,6 +2309,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1871,6 +2375,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1917,6 +2441,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1963,6 +2507,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2013,6 +2577,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2059,6 +2643,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2105,6 +2709,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2151,6 +2775,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2197,6 +2841,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2243,6 +2907,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2289,6 +2973,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2335,6 +3039,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2381,6 +3105,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2427,6 +3171,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2477,6 +3241,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2523,6 +3307,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2569,6 +3373,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2615,6 +3439,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2661,6 +3505,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2707,6 +3571,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2753,6 +3637,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2799,6 +3703,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2845,6 +3769,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2891,6 +3835,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2937,6 +3901,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2983,6 +3967,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3029,6 +4033,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3075,6 +4099,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3121,6 +4165,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3171,6 +4235,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3221,6 +4305,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3267,6 +4371,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3317,6 +4441,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3367,6 +4511,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3413,6 +4577,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3459,6 +4643,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3505,6 +4709,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3551,6 +4775,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3601,6 +4845,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3647,6 +4911,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3697,6 +4981,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3747,6 +5051,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3793,6 +5117,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3839,6 +5183,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3889,6 +5253,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3935,6 +5319,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3981,6 +5385,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4027,6 +5451,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4073,6 +5517,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4119,6 +5583,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4165,6 +5649,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4211,6 +5715,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4257,6 +5781,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4303,6 +5847,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4349,6 +5913,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4395,6 +5979,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4445,6 +6049,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4491,6 +6115,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4537,6 +6181,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4583,6 +6247,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4629,6 +6313,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4675,6 +6379,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4721,6 +6445,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4767,6 +6511,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4813,6 +6577,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4859,6 +6643,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4905,6 +6709,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4951,6 +6775,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4997,6 +6841,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5043,6 +6907,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5093,6 +6977,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5143,6 +7047,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5189,6 +7113,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5235,6 +7179,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5270,7 +7234,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5281,6 +7245,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5327,6 +7311,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5373,6 +7377,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5419,6 +7443,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5465,6 +7509,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5511,6 +7575,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5561,6 +7645,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5607,6 +7711,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5653,6 +7777,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5699,6 +7843,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5745,6 +7909,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5791,6 +7975,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5837,6 +8041,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5883,6 +8107,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5929,6 +8173,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5975,6 +8239,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6021,6 +8305,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6067,6 +8371,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6113,6 +8437,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6159,6 +8503,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6205,6 +8569,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6251,6 +8635,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6297,6 +8701,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6343,6 +8767,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6389,6 +8833,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6435,6 +8899,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6481,6 +8965,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6527,6 +9031,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6573,6 +9097,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6619,6 +9163,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6665,6 +9229,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6711,6 +9295,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6757,6 +9361,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6803,6 +9427,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6849,6 +9493,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6895,6 +9559,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6945,6 +9629,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6991,6 +9695,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7037,6 +9761,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7087,6 +9831,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7133,6 +9897,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7179,6 +9963,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7225,6 +10029,26 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7271,6 +10095,26 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7317,6 +10161,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7367,6 +10231,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7413,6 +10297,26 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7459,6 +10363,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7509,6 +10433,26 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7559,6 +10503,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7609,6 +10573,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7659,6 +10643,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7705,6 +10709,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7751,6 +10775,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7797,6 +10841,26 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7843,6 +10907,26 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7889,6 +10973,26 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7935,6 +11039,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7981,6 +11105,26 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8027,6 +11171,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8073,6 +11237,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8119,6 +11303,26 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8165,6 +11369,26 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8211,6 +11435,26 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8257,6 +11501,26 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8303,6 +11567,26 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8349,6 +11633,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8395,6 +11699,26 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8441,6 +11765,26 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8487,6 +11831,26 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8533,6 +11897,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8579,6 +11963,26 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8625,6 +12029,26 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8671,6 +12095,26 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8721,6 +12165,26 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8771,6 +12235,26 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8821,6 +12305,26 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8867,6 +12371,26 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8913,6 +12437,26 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8959,6 +12503,26 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9005,6 +12569,26 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9051,6 +12635,26 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9097,6 +12701,26 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9143,6 +12767,26 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9189,6 +12833,26 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9235,6 +12899,26 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9285,6 +12969,26 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9331,6 +13035,26 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9377,6 +13101,26 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9423,6 +13167,26 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9469,6 +13233,26 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9515,6 +13299,26 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9561,6 +13365,26 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9607,6 +13431,26 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9653,6 +13497,26 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9699,6 +13563,26 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9745,6 +13629,26 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9791,6 +13695,26 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9837,6 +13761,26 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9887,6 +13831,26 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9933,6 +13897,26 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9979,6 +13963,26 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10025,6 +14029,26 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10071,6 +14095,26 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10117,6 +14161,26 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10163,6 +14227,26 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10209,6 +14293,26 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10255,6 +14359,26 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10301,6 +14425,26 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10347,6 +14491,26 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10397,6 +14561,26 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10443,6 +14627,26 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10489,6 +14693,26 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10535,6 +14759,26 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10585,6 +14829,26 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10631,6 +14895,26 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10677,6 +14961,26 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10723,6 +15027,26 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10769,6 +15093,26 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10815,6 +15159,26 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10861,6 +15225,26 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10907,6 +15291,26 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10953,6 +15357,26 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10999,6 +15423,26 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11045,6 +15489,26 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11091,6 +15555,26 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11137,6 +15621,26 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11183,6 +15687,26 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11229,6 +15753,26 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11275,6 +15819,26 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11321,6 +15885,26 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11367,6 +15951,26 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11413,6 +16017,26 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11463,6 +16087,26 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11509,6 +16153,26 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11555,6 +16219,26 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11601,6 +16285,26 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11647,6 +16351,26 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11693,6 +16417,26 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11739,6 +16483,26 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11785,6 +16549,26 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11831,6 +16615,26 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11877,6 +16681,26 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11923,6 +16747,26 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L243" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11969,6 +16813,26 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12015,6 +16879,26 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12061,6 +16945,26 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12107,6 +17011,26 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12153,6 +17077,26 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12199,6 +17143,26 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12245,6 +17209,26 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12291,6 +17275,26 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12337,6 +17341,26 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12383,6 +17407,26 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12429,6 +17473,26 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12475,6 +17539,26 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12521,6 +17605,26 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12567,6 +17671,26 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12613,6 +17737,26 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12659,6 +17803,26 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12705,6 +17869,26 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12751,6 +17935,26 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12797,6 +18001,26 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12843,6 +18067,26 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12889,6 +18133,26 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12935,6 +18199,26 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12981,13 +18265,33 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -13119,7 +18423,7 @@
           <t>A | 2059呎 (3房)
 $8888万
 $43,167/呎
-(16年-09月)</t>
+(16年-09月-01日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -13127,7 +18431,7 @@
           <t>B | 2093呎 (3房)
 $10528万
 $50,301/呎
-(17年-01月)</t>
+(17年-01月-12日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -13143,7 +18447,7 @@
           <t>D | 1709呎 (3房)
 $6300万
 $36,864/呎
-(16年-09月)</t>
+(16年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -13158,7 +18462,7 @@
           <t>A | 1058呎 (3房)
 $52262万
 $493,971/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -13166,7 +18470,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -13174,7 +18478,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -13182,7 +18486,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13197,7 +18501,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -13205,7 +18509,7 @@
           <t>B | 1083呎 (3房)
 $52262万
 $482,568/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -13213,7 +18517,7 @@
           <t>C | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -13221,7 +18525,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13260,7 +18564,7 @@
           <t>D | 855呎 (3房)
 $2550万
 $29,825/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
     </row>
@@ -13275,7 +18579,7 @@
           <t>A | 1052呎 (3房)
 $3467万
 $32,956/呎
-(16年-07月)</t>
+(16年-07月-11日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -13283,7 +18587,7 @@
           <t>B | 1070呎 (3房)
 $3130万
 $29,252/呎
-(11年-02月)</t>
+(11年-02月-20日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -13291,7 +18595,7 @@
           <t>C | 855呎 (3房)
 $2866万
 $33,518/呎
-(15年-10月)</t>
+(15年-10月-18日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -13299,7 +18603,7 @@
           <t>D | 855呎 (3房)
 $2643万
 $30,917/呎
-(15年-11月)</t>
+(15年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -13314,7 +18618,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -13322,7 +18626,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -13330,7 +18634,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -13338,7 +18642,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13361,7 +18665,7 @@
           <t>B | 1070呎 (3房)
 $3250万
 $30,374/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -13369,7 +18673,7 @@
           <t>C | 855呎 (3房)
 $2830万
 $33,099/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -13377,7 +18681,7 @@
           <t>D | 855呎 (3房)
 $2620万
 $30,643/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -13392,7 +18696,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -13400,7 +18704,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -13408,7 +18712,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -13416,7 +18720,7 @@
           <t>D | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13431,7 +18735,7 @@
           <t>A | 1052呎 (3房)
 $3426万
 $32,564/呎
-(16年-10月)</t>
+(16年-10月-06日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -13439,7 +18743,7 @@
           <t>B | 1083呎 (3房)
 $2950万
 $27,239/呎
-(11年-01月)</t>
+(11年-01月-09日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -13447,7 +18751,7 @@
           <t>C | 855呎 (3房)
 $2833万
 $33,133/呎
-(16年-06月)</t>
+(16年-06月-13日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -13455,7 +18759,7 @@
           <t>D | 855呎 (3房)
 $2640万
 $30,871/呎
-(16年-10月)</t>
+(16年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -13470,7 +18774,7 @@
           <t>A | 1052呎 (3房)
 $3100万
 $29,468/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -13478,7 +18782,7 @@
           <t>B | 1070呎 (3房)
 $3418万
 $31,944/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -13494,7 +18798,7 @@
           <t>D | 855呎 (3房)
 $2430万
 $28,421/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -13509,7 +18813,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -13517,7 +18821,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -13525,7 +18829,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -13533,7 +18837,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13548,7 +18852,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -13556,7 +18860,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -13564,7 +18868,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -13572,7 +18876,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13587,7 +18891,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -13595,7 +18899,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -13603,7 +18907,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -13611,7 +18915,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13634,7 +18938,7 @@
           <t>B | 1052呎 (3房)
 $1269万
 $12,064/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -13665,7 +18969,7 @@
           <t>A | 1032呎 (3房)
 $3030万
 $29,360/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -13673,7 +18977,7 @@
           <t>B | 1052呎 (3房)
 $1255万
 $11,931/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -13681,7 +18985,7 @@
           <t>C | 841呎 (3房)
 $2550万
 $30,321/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -13712,7 +19016,7 @@
           <t>B | 1052呎 (3房)
 $1305万
 $12,405/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -13728,7 +19032,7 @@
           <t>D | 840呎 (2房)
 $1008万
 $11,994/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -13751,7 +19055,7 @@
           <t>B | 1052呎 (3房)
 $2750万
 $26,141/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -13759,7 +19063,7 @@
           <t>C | 865呎 (3房)
 $2370万
 $27,399/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -13782,7 +19086,7 @@
           <t>A | 1032呎 (3房)
 $2280万
 $22,093/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -13790,7 +19094,7 @@
           <t>B | 1065呎 (3房)
 $2553万
 $23,972/呎
-(11年-01月)</t>
+(11年-01月-11日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -13798,7 +19102,7 @@
           <t>C | 841呎 (3房)
 $2578万
 $30,649/呎
-(15年-10月)</t>
+(15年-10月-04日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -13806,7 +19110,7 @@
           <t>D | 840呎 (2房)
 $2339万
 $27,842/呎
-(16年-06月)</t>
+(16年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -13821,7 +19125,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -13829,7 +19133,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -13837,7 +19141,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -13845,7 +19149,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13868,7 +19172,7 @@
           <t>B | 1052呎 (3房)
 $2800万
 $26,616/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -13876,7 +19180,7 @@
           <t>C | 841呎 (3房)
 $2350万
 $27,943/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -13884,7 +19188,7 @@
           <t>D | 840呎 (2房)
 $889万
 $10,585/呎
-(02年-01月)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -13899,7 +19203,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -13907,7 +19211,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -13915,7 +19219,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -13923,7 +19227,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13938,7 +19242,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -13946,7 +19250,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -13954,7 +19258,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -13962,7 +19266,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -13977,7 +19281,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -13985,7 +19289,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -13993,7 +19297,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -14001,7 +19305,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -14016,7 +19320,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -14040,7 +19344,7 @@
           <t>D | 840呎 (2房)
 $894万
 $10,637/呎
-(02年-02月)</t>
+(02年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -14055,7 +19359,7 @@
           <t>A | 1032呎 (3房)
 $998万
 $9,671/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -14063,7 +19367,7 @@
           <t>B | 1042呎 (3房)
 $2680万
 $25,720/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -14071,7 +19375,7 @@
           <t>C | 841呎 (3房)
 $2370万
 $28,181/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -14079,7 +19383,7 @@
           <t>D | 840呎 (2房)
 $843万
 $10,032/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -14102,7 +19406,7 @@
           <t>B | 1056呎 (3房)
 $52262万
 $494,906/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -14110,7 +19414,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -14118,7 +19422,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -14133,7 +19437,7 @@
           <t>A | 620呎 (2房)
 $550万
 $8,863/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -14141,7 +19445,7 @@
           <t>B | 1042呎 (3房)
 $2088万
 $20,038/呎
-(11年-01月)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -14149,7 +19453,7 @@
           <t>C | 841呎 (3房)
 $1960万
 $23,306/呎
-(11年-06月)</t>
+(11年-06月-16日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -14157,7 +19461,7 @@
           <t>D | 840呎 (2房)
 $760万
 $9,048/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -14172,7 +19476,7 @@
           <t>A | 618呎 (2房)
 $465万
 $7,518/呎
-(01年-12月)</t>
+(01年-12月-30日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -14180,7 +19484,7 @@
           <t>B | 1042呎 (3房)
 $1049万
 $10,067/呎
-(02年-03月)</t>
+(02年-03月-25日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -14188,7 +19492,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,774/呎
-(15年-09月)</t>
+(15年-09月-28日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -14196,7 +19500,7 @@
           <t>D | 840呎 (2房)
 $1670万
 $19,881/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -14211,7 +19515,7 @@
           <t>A | 618呎 (2房)
 $482万
 $7,799/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -14219,7 +19523,7 @@
           <t>B | 1042呎 (3房)
 $2188万
 $20,998/呎
-(11年-01月)</t>
+(11年-01月-20日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -14227,7 +19531,7 @@
           <t>C | 841呎 (3房)
 $881万
 $10,476/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -14235,7 +19539,7 @@
           <t>D | 840呎 (2房)
 $785万
 $9,345/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -14250,7 +19554,7 @@
           <t>A | 618呎 (2房)
 $529万
 $8,560/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -14258,7 +19562,7 @@
           <t>B | 1042呎 (3房)
 $2210万
 $21,209/呎
-(11年-02月)</t>
+(11年-02月-28日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -14266,7 +19570,7 @@
           <t>C | 841呎 (3房)
 $2034万
 $24,186/呎
-(16年-10月)</t>
+(16年-10月-13日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -14274,7 +19578,7 @@
           <t>D | 840呎 (2房)
 $690万
 $8,211/呎
-(02年-02月)</t>
+(02年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -14289,7 +19593,7 @@
           <t>A | 618呎 (2房)
 $520万
 $8,414/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -14297,7 +19601,7 @@
           <t>B | 1056呎 (3房)
 $2158万
 $20,438/呎
-(11年-03月)</t>
+(11年-03月-21日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -14305,7 +19609,7 @@
           <t>C | 841呎 (3房)
 $2040万
 $24,257/呎
-(16年-06月)</t>
+(16年-06月-13日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -14313,7 +19617,7 @@
           <t>D | 840呎 (2房)
 $730万
 $8,692/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -14328,7 +19632,7 @@
           <t>A | 618呎 (2房)
 $433万
 $7,010/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -14336,7 +19640,7 @@
           <t>B | 1042呎 (3房)
 $52262万
 $501,556/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -14344,7 +19648,7 @@
           <t>C | 841呎 (3房)
 $4719万
 $56,108/呎
-(15年-12月)</t>
+(15年-12月-23日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -14352,7 +19656,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,883/呎
-(01年-12月)</t>
+(01年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -14368,7 +19672,7 @@
           <t>B | 1042呎 (3房)
 $2561万
 $24,579/呎
-(15年-11月)</t>
+(15年-11月-19日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -14376,7 +19680,7 @@
           <t>C | 841呎 (3房)
 $1911万
 $22,717/呎
-(15年-11月)</t>
+(15年-11月-17日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr"/>
@@ -14523,7 +19827,7 @@
           <t>B | 1995呎 (3房)
 $4300万
 $21,554/呎
-(07年-06月)</t>
+(07年-06月-28日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -14531,7 +19835,7 @@
           <t>C | 1366呎 (3房)
 $2963万
 $21,690/呎
-(06年-08月)</t>
+(06年-08月-16日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -14539,7 +19843,7 @@
           <t>D | 1366呎 (3房)
 $3330万
 $24,378/呎
-(07年-08月)</t>
+(07年-08月-23日)</t>
         </is>
       </c>
     </row>
@@ -14554,7 +19858,7 @@
           <t>A | 2181呎 (3房)
 $7618万
 $34,928/呎
-(16年-07月)</t>
+(16年-07月-13日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -14570,7 +19874,7 @@
           <t>C | 1412呎 (3房)
 $2980万
 $21,105/呎
-(07年-08月)</t>
+(07年-08月-22日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -14578,7 +19882,7 @@
           <t>D | 1412呎 (3房)
 $6110万
 $43,275/呎
-(15年-09月)</t>
+(15年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -14593,7 +19897,7 @@
           <t>A | 1070呎 (3房)
 $2900万
 $27,103/呎
-(11年-03月)</t>
+(11年-03月-20日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -14601,7 +19905,7 @@
           <t>B | 1052呎 (3房)
 $3442万
 $32,721/呎
-(16年-01月)</t>
+(16年-01月-06日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -14609,7 +19913,7 @@
           <t>C | 855呎 (3房)
 $2798万
 $32,722/呎
-(15年-12月)</t>
+(15年-12月-27日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -14617,7 +19921,7 @@
           <t>D | 855呎 (3房)
 $2410万
 $28,187/呎
-(11年-05月)</t>
+(11年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -14640,7 +19944,7 @@
           <t>B | 1052呎 (3房)
 $3300万
 $31,369/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -14648,7 +19952,7 @@
           <t>C | 855呎 (3房)
 $2590万
 $30,292/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -14671,7 +19975,7 @@
           <t>A | 1070呎 (3房)
 $1363万
 $12,738/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -14710,7 +20014,7 @@
           <t>A | 1070呎 (3房)
 $3860万
 $36,075/呎
-(17年-07月)</t>
+(17年-07月-30日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -14718,7 +20022,7 @@
           <t>B | 1052呎 (3房)
 $2789万
 $26,510/呎
-(11年-06月)</t>
+(11年-06月-27日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -14726,7 +20030,7 @@
           <t>C | 855呎 (3房)
 $2511万
 $29,371/呎
-(11年-06月)</t>
+(11年-06月-27日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -14734,7 +20038,7 @@
           <t>D | 855呎 (3房)
 $2850万
 $33,333/呎
-(17年-07月)</t>
+(17年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -14749,7 +20053,7 @@
           <t>A | 1070呎 (3房)
 $2925万
 $27,336/呎
-(11年-06月)</t>
+(11年-06月-14日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -14757,7 +20061,7 @@
           <t>B | 1052呎 (3房)
 $2663万
 $25,312/呎
-(11年-04月)</t>
+(11年-04月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -14765,7 +20069,7 @@
           <t>C | 855呎 (3房)
 $2700万
 $31,579/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -14773,7 +20077,7 @@
           <t>D | 855呎 (3房)
 $2630万
 $30,760/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -14788,7 +20092,7 @@
           <t>A | 1070呎 (3房)
 $2650万
 $24,766/呎
-(10年-12月)</t>
+(10年-12月-30日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -14796,7 +20100,7 @@
           <t>B | 1052呎 (3房)
 $2580万
 $24,525/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -14804,7 +20108,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-12月)</t>
+(15年-12月-01日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -14812,7 +20116,7 @@
           <t>D | 855呎 (3房)
 $2619万
 $30,628/呎
-(15年-11月)</t>
+(15年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -14827,7 +20131,7 @@
           <t>A | 1083呎 (3房)
 $1288万
 $11,893/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -14835,7 +20139,7 @@
           <t>B | 1052呎 (3房)
 $2520万
 $23,954/呎
-(11年-01月)</t>
+(11年-01月-12日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -14843,7 +20147,7 @@
           <t>C | 855呎 (3房)
 $4719万
 $55,189/呎
-(15年-12月)</t>
+(15年-12月-23日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -14851,7 +20155,7 @@
           <t>D | 855呎 (3房)
 $2602万
 $30,436/呎
-(15年-11月)</t>
+(15年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -14866,7 +20170,7 @@
           <t>A | 1070呎 (3房)
 $2715万
 $25,374/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -14874,7 +20178,7 @@
           <t>B | 1052呎 (3房)
 $3372万
 $32,055/呎
-(16年-06月)</t>
+(16年-06月-21日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -14882,7 +20186,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-09月)</t>
+(15年-09月-29日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -14890,7 +20194,7 @@
           <t>D | 855呎 (3房)
 $2265万
 $26,491/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -14929,7 +20233,7 @@
           <t>D | 855呎 (3房)
 $988万
 $11,557/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -14944,7 +20248,7 @@
           <t>A | 1052呎 (3房)
 $3376万
 $32,095/呎
-(16年-06月)</t>
+(16年-06月-13日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -14952,7 +20256,7 @@
           <t>B | 1032呎 (3房)
 $2448万
 $23,721/呎
-(11年-05月)</t>
+(11年-05月-29日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -14960,7 +20264,7 @@
           <t>C | 841呎 (3房)
 $1792万
 $21,307/呎
-(08年-03月)</t>
+(08年-03月-26日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -14968,7 +20272,7 @@
           <t>D | 841呎 (3房)
 $2560万
 $30,440/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -14983,7 +20287,7 @@
           <t>A | 1052呎 (3房)
 $1192万
 $11,335/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -14991,7 +20295,7 @@
           <t>B | 1032呎 (3房)
 $2250万
 $21,802/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -14999,7 +20303,7 @@
           <t>C | 841呎 (3房)
 $2080万
 $24,732/呎
-(11年-01月)</t>
+(11年-01月-26日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -15007,7 +20311,7 @@
           <t>D | 841呎 (3房)
 $2154万
 $25,612/呎
-(11年-06月)</t>
+(11年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -15022,7 +20326,7 @@
           <t>A | 1065呎 (3房)
 $2350万
 $22,066/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -15030,7 +20334,7 @@
           <t>B | 1032呎 (3房)
 $2210万
 $21,415/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -15046,7 +20350,7 @@
           <t>D | 865呎 (3房)
 $920万
 $10,631/呎
-(02年-04月)</t>
+(02年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -15061,7 +20365,7 @@
           <t>A | 1052呎 (3房)
 $1167万
 $11,093/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -15069,7 +20373,7 @@
           <t>B | 1032呎 (3房)
 $2160万
 $20,930/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -15077,7 +20381,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,768/呎
-(11年-03月)</t>
+(11年-03月-08日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -15085,7 +20389,7 @@
           <t>D | 841呎 (3房)
 $2118万
 $25,184/呎
-(11年-06月)</t>
+(11年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -15100,7 +20404,7 @@
           <t>A | 1052呎 (3房)
 $1210万
 $11,507/呎
-(02年-01月)</t>
+(02年-01月-16日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -15108,7 +20412,7 @@
           <t>B | 1038呎 (3房)
 $2160万
 $20,809/呎
-(11年-01月)</t>
+(11年-01月-06日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -15116,7 +20420,7 @@
           <t>C | 840呎 (2房)
 $1960万
 $23,333/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -15124,7 +20428,7 @@
           <t>D | 841呎 (3房)
 $2380万
 $28,299/呎
-(15年-11月)</t>
+(15年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -15139,7 +20443,7 @@
           <t>A | 1052呎 (3房)
 $1197万
 $11,378/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -15155,7 +20459,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -15163,7 +20467,7 @@
           <t>D | 841呎 (3房)
 $2000万
 $23,781/呎
-(11年-03月)</t>
+(11年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -15178,7 +20482,7 @@
           <t>A | 1064呎 (3房)
 $1125万
 $10,573/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -15186,7 +20490,7 @@
           <t>B | 1032呎 (3房)
 $2100万
 $20,349/呎
-(11年-01月)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -15194,7 +20498,7 @@
           <t>C | 840呎 (2房)
 $1900万
 $22,619/呎
-(11年-01月)</t>
+(11年-01月-13日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -15202,7 +20506,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,253/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -15217,7 +20521,7 @@
           <t>A | 1052呎 (3房)
 $1140万
 $10,833/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -15225,7 +20529,7 @@
           <t>B | 1038呎 (3房)
 $2140万
 $20,617/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -15233,7 +20537,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月)</t>
+(11年-01月-30日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -15241,7 +20545,7 @@
           <t>D | 841呎 (3房)
 $2363万
 $28,103/呎
-(15年-11月)</t>
+(15年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -15256,7 +20560,7 @@
           <t>A | 1052呎 (3房)
 $1015万
 $9,651/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -15264,7 +20568,7 @@
           <t>B | 1032呎 (3房)
 $953万
 $9,232/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -15280,7 +20584,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,249/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -15295,7 +20599,7 @@
           <t>A | 1052呎 (3房)
 $1064万
 $10,113/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -15303,7 +20607,7 @@
           <t>B | 1032呎 (3房)
 $1950万
 $18,895/呎
-(10年-12月)</t>
+(10年-12月-30日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -15319,7 +20623,7 @@
           <t>D | 841呎 (3房)
 $896万
 $10,649/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -15334,7 +20638,7 @@
           <t>A | 1064呎 (3房)
 $1061万
 $9,976/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -15342,7 +20646,7 @@
           <t>B | 1032呎 (3房)
 $1938万
 $18,779/呎
-(11年-01月)</t>
+(11年-01月-13日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -15350,7 +20654,7 @@
           <t>C | 863呎 (2房)
 $1810万
 $20,973/呎
-(11年-01月)</t>
+(11年-01月-10日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -15358,7 +20662,7 @@
           <t>D | 841呎 (3房)
 $1838万
 $21,855/呎
-(11年-01月)</t>
+(11年-01月-31日)</t>
         </is>
       </c>
     </row>
@@ -15373,7 +20677,7 @@
           <t>A | 1064呎 (3房)
 $1040万
 $9,773/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -15381,7 +20685,7 @@
           <t>B | 1032呎 (3房)
 $1900万
 $18,411/呎
-(10年-12月)</t>
+(10年-12月-28日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -15389,7 +20693,7 @@
           <t>C | 840呎 (2房)
 $1740万
 $20,714/呎
-(11年-01月)</t>
+(11年-01月-11日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -15397,7 +20701,7 @@
           <t>D | 841呎 (3房)
 $1790万
 $21,284/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -15412,7 +20716,7 @@
           <t>A | 1065呎 (3房)
 $942万
 $8,848/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -15420,7 +20724,7 @@
           <t>B | 1032呎 (3房)
 $1867万
 $18,094/呎
-(10年-12月)</t>
+(10年-12月-19日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -15428,7 +20732,7 @@
           <t>C | 865呎 (2房)
 $1723万
 $19,916/呎
-(10年-12月)</t>
+(10年-12月-19日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -15436,7 +20740,7 @@
           <t>D | 841呎 (3房)
 $913万
 $10,856/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -15451,7 +20755,7 @@
           <t>A | 1042呎 (3房)
 $1065万
 $10,221/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -15459,7 +20763,7 @@
           <t>B | 1032呎 (3房)
 $1918万
 $18,585/呎
-(11年-01月)</t>
+(11年-01月-05日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -15467,7 +20771,7 @@
           <t>C | 840呎 (2房)
 $881万
 $10,492/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -15475,7 +20779,7 @@
           <t>D | 841呎 (3房)
 $733万
 $8,721/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -15490,7 +20794,7 @@
           <t>A | 1042呎 (3房)
 $1015万
 $9,740/呎
-(02年-03月)</t>
+(02年-03月-15日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -15498,7 +20802,7 @@
           <t>B | 1039呎 (3房)
 $892万
 $8,586/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -15506,7 +20810,7 @@
           <t>C | 840呎 (2房)
 $1780万
 $21,190/呎
-(11年-01月)</t>
+(11年-01月-20日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -15529,7 +20833,7 @@
           <t>A | 1056呎 (3房)
 $832万
 $7,877/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -15537,7 +20841,7 @@
           <t>B | 1032呎 (3房)
 $840万
 $8,140/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -15545,7 +20849,7 @@
           <t>C | 840呎 (2房)
 $750万
 $8,935/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -15553,7 +20857,7 @@
           <t>D | 865呎 (3房)
 $769万
 $8,890/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -15568,7 +20872,7 @@
           <t>A | 1042呎 (3房)
 $858万
 $8,234/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -15576,7 +20880,7 @@
           <t>B | 618呎 (2房)
 $487万
 $7,880/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -15584,7 +20888,7 @@
           <t>C | 840呎 (2房)
 $791万
 $9,417/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -15592,7 +20896,7 @@
           <t>D | 841呎 (2房)
 $733万
 $8,717/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -15607,7 +20911,7 @@
           <t>A | 1042呎 (3房)
 $891万
 $8,548/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -15615,7 +20919,7 @@
           <t>B | 619呎 (2房)
 $486万
 $7,851/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -15623,7 +20927,7 @@
           <t>C | 840呎 (2房)
 $723万
 $8,607/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -15631,7 +20935,7 @@
           <t>D | 841呎 (2房)
 $715万
 $8,501/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -15646,7 +20950,7 @@
           <t>A | 1042呎 (3房)
 $828万
 $7,947/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -15654,7 +20958,7 @@
           <t>B | 618呎 (2房)
 $481万
 $7,783/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -15662,7 +20966,7 @@
           <t>C | 840呎 (2房)
 $709万
 $8,445/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -15670,7 +20974,7 @@
           <t>D | 865呎 (2房)
 $754万
 $8,716/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -15685,7 +20989,7 @@
           <t>A | 1042呎 (3房)
 $866万
 $8,311/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -15693,7 +20997,7 @@
           <t>B | 618呎 (2房)
 $426万
 $6,893/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -15701,7 +21005,7 @@
           <t>C | 840呎 (2房)
 $650万
 $7,736/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -15709,7 +21013,7 @@
           <t>D | 840呎 (2房)
 $1490万
 $17,738/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -15724,7 +21028,7 @@
           <t>A | 1056呎 (3房)
 $855万
 $8,097/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -15732,7 +21036,7 @@
           <t>B | 618呎 (2房)
 $456万
 $7,385/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -15740,7 +21044,7 @@
           <t>C | 840呎 (2房)
 $724万
 $8,625/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -15748,7 +21052,7 @@
           <t>D | 840呎 (2房)
 $718万
 $8,548/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -15763,7 +21067,7 @@
           <t>A | 1042呎 (3房)
 $760万
 $7,295/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -15771,7 +21075,7 @@
           <t>B | 618呎 (2房)
 $373万
 $6,042/呎
-(01年-12月)</t>
+(01年-12月-30日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -15779,7 +21083,7 @@
           <t>C | 840呎 (2房)
 $707万
 $8,417/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -15787,7 +21091,7 @@
           <t>D | 840呎 (2房)
 $667万
 $7,936/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -15802,7 +21106,7 @@
           <t>A | 1042呎 (3房)
 $732万
 $7,022/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr"/>
@@ -15812,7 +21116,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,875/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,11 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,6 +270,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1691,7 +1699,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1701,12 +1709,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1716,12 +1724,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1731,7 +1739,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18366,22 +18374,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -18543,12 +18551,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1083呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -19666,7 +19674,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr"/>
+      <c r="B37" s="23" t="inlineStr"/>
       <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 1042呎 (3房)
@@ -19683,7 +19691,7 @@
 (15年-11月-17日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr"/>
+      <c r="E37" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21109,8 +21117,8 @@
 (01年-12月-28日)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr"/>
-      <c r="D38" s="22" t="inlineStr"/>
+      <c r="C38" s="23" t="inlineStr"/>
+      <c r="D38" s="23" t="inlineStr"/>
       <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 840呎 (2房)

--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -18431,7 +18431,7 @@
           <t>A | 2059呎 (3房)
 $8888万
 $43,167/呎
-(16年-09月-01日)</t>
+(16年-09月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -18439,7 +18439,7 @@
           <t>B | 2093呎 (3房)
 $10528万
 $50,301/呎
-(17年-01月-12日)</t>
+(17年-01月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -18455,7 +18455,7 @@
           <t>D | 1709呎 (3房)
 $6300万
 $36,864/呎
-(16年-09月-15日)</t>
+(16年-09月)</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
           <t>A | 1058呎 (3房)
 $52262万
 $493,971/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -18478,7 +18478,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -18486,7 +18486,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -18494,7 +18494,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -18509,7 +18509,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -18517,7 +18517,7 @@
           <t>B | 1083呎 (3房)
 $52262万
 $482,568/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -18525,7 +18525,7 @@
           <t>C | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -18533,7 +18533,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -18572,7 +18572,7 @@
           <t>D | 855呎 (3房)
 $2550万
 $29,825/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -18587,7 +18587,7 @@
           <t>A | 1052呎 (3房)
 $3467万
 $32,956/呎
-(16年-07月-11日)</t>
+(16年-07月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -18595,7 +18595,7 @@
           <t>B | 1070呎 (3房)
 $3130万
 $29,252/呎
-(11年-02月-20日)</t>
+(11年-02月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -18603,7 +18603,7 @@
           <t>C | 855呎 (3房)
 $2866万
 $33,518/呎
-(15年-10月-18日)</t>
+(15年-10月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -18611,7 +18611,7 @@
           <t>D | 855呎 (3房)
 $2643万
 $30,917/呎
-(15年-11月-24日)</t>
+(15年-11月)</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -18634,7 +18634,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -18642,7 +18642,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -18650,7 +18650,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -18673,7 +18673,7 @@
           <t>B | 1070呎 (3房)
 $3250万
 $30,374/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -18681,7 +18681,7 @@
           <t>C | 855呎 (3房)
 $2830万
 $33,099/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -18689,7 +18689,7 @@
           <t>D | 855呎 (3房)
 $2620万
 $30,643/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -18704,7 +18704,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -18712,7 +18712,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -18720,7 +18720,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -18728,7 +18728,7 @@
           <t>D | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
           <t>A | 1052呎 (3房)
 $3426万
 $32,564/呎
-(16年-10月-06日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -18751,7 +18751,7 @@
           <t>B | 1083呎 (3房)
 $2950万
 $27,239/呎
-(11年-01月-09日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -18759,7 +18759,7 @@
           <t>C | 855呎 (3房)
 $2833万
 $33,133/呎
-(16年-06月-13日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -18767,7 +18767,7 @@
           <t>D | 855呎 (3房)
 $2640万
 $30,871/呎
-(16年-10月-31日)</t>
+(16年-10月)</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
           <t>A | 1052呎 (3房)
 $3100万
 $29,468/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -18790,7 +18790,7 @@
           <t>B | 1070呎 (3房)
 $3418万
 $31,944/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -18806,7 +18806,7 @@
           <t>D | 855呎 (3房)
 $2430万
 $28,421/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -18821,7 +18821,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -18829,7 +18829,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -18837,7 +18837,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -18845,7 +18845,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18860,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -18868,7 +18868,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -18876,7 +18876,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -18884,7 +18884,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -18899,7 +18899,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -18907,7 +18907,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -18915,7 +18915,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -18923,7 +18923,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
           <t>B | 1052呎 (3房)
 $1269万
 $12,064/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -18977,7 +18977,7 @@
           <t>A | 1032呎 (3房)
 $3030万
 $29,360/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -18985,7 +18985,7 @@
           <t>B | 1052呎 (3房)
 $1255万
 $11,931/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -18993,7 +18993,7 @@
           <t>C | 841呎 (3房)
 $2550万
 $30,321/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -19024,7 +19024,7 @@
           <t>B | 1052呎 (3房)
 $1305万
 $12,405/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -19040,7 +19040,7 @@
           <t>D | 840呎 (2房)
 $1008万
 $11,994/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
           <t>B | 1052呎 (3房)
 $2750万
 $26,141/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -19071,7 +19071,7 @@
           <t>C | 865呎 (3房)
 $2370万
 $27,399/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -19094,7 +19094,7 @@
           <t>A | 1032呎 (3房)
 $2280万
 $22,093/呎
-(11年-01月-18日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -19102,7 +19102,7 @@
           <t>B | 1065呎 (3房)
 $2553万
 $23,972/呎
-(11年-01月-11日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -19110,7 +19110,7 @@
           <t>C | 841呎 (3房)
 $2578万
 $30,649/呎
-(15年-10月-04日)</t>
+(15年-10月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -19118,7 +19118,7 @@
           <t>D | 840呎 (2房)
 $2339万
 $27,842/呎
-(16年-06月-07日)</t>
+(16年-06月)</t>
         </is>
       </c>
     </row>
@@ -19133,7 +19133,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -19141,7 +19141,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -19149,7 +19149,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -19157,7 +19157,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -19180,7 +19180,7 @@
           <t>B | 1052呎 (3房)
 $2800万
 $26,616/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -19188,7 +19188,7 @@
           <t>C | 841呎 (3房)
 $2350万
 $27,943/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -19196,7 +19196,7 @@
           <t>D | 840呎 (2房)
 $889万
 $10,585/呎
-(02年-01月-10日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -19211,7 +19211,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -19219,7 +19219,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -19227,7 +19227,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -19235,7 +19235,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -19258,7 +19258,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -19266,7 +19266,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -19274,7 +19274,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -19289,7 +19289,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -19297,7 +19297,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -19305,7 +19305,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -19313,7 +19313,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -19328,7 +19328,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -19352,7 +19352,7 @@
           <t>D | 840呎 (2房)
 $894万
 $10,637/呎
-(02年-02月-15日)</t>
+(02年-02月)</t>
         </is>
       </c>
     </row>
@@ -19367,7 +19367,7 @@
           <t>A | 1032呎 (3房)
 $998万
 $9,671/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -19375,7 +19375,7 @@
           <t>B | 1042呎 (3房)
 $2680万
 $25,720/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -19383,7 +19383,7 @@
           <t>C | 841呎 (3房)
 $2370万
 $28,181/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -19391,7 +19391,7 @@
           <t>D | 840呎 (2房)
 $843万
 $10,032/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
     </row>
@@ -19414,7 +19414,7 @@
           <t>B | 1056呎 (3房)
 $52262万
 $494,906/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -19422,7 +19422,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -19430,7 +19430,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -19445,7 +19445,7 @@
           <t>A | 620呎 (2房)
 $550万
 $8,863/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -19453,7 +19453,7 @@
           <t>B | 1042呎 (3房)
 $2088万
 $20,038/呎
-(11年-01月-17日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -19461,7 +19461,7 @@
           <t>C | 841呎 (3房)
 $1960万
 $23,306/呎
-(11年-06月-16日)</t>
+(11年-06月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -19469,7 +19469,7 @@
           <t>D | 840呎 (2房)
 $760万
 $9,048/呎
-(02年-01月-07日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
           <t>A | 618呎 (2房)
 $465万
 $7,518/呎
-(01年-12月-30日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -19492,7 +19492,7 @@
           <t>B | 1042呎 (3房)
 $1049万
 $10,067/呎
-(02年-03月-25日)</t>
+(02年-03月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -19500,7 +19500,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,774/呎
-(15年-09月-28日)</t>
+(15年-09月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -19508,7 +19508,7 @@
           <t>D | 840呎 (2房)
 $1670万
 $19,881/呎
-(11年-01月-23日)</t>
+(11年-01月)</t>
         </is>
       </c>
     </row>
@@ -19523,7 +19523,7 @@
           <t>A | 618呎 (2房)
 $482万
 $7,799/呎
-(01年-12月-27日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -19531,7 +19531,7 @@
           <t>B | 1042呎 (3房)
 $2188万
 $20,998/呎
-(11年-01月-20日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -19539,7 +19539,7 @@
           <t>C | 841呎 (3房)
 $881万
 $10,476/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -19547,7 +19547,7 @@
           <t>D | 840呎 (2房)
 $785万
 $9,345/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19562,7 @@
           <t>A | 618呎 (2房)
 $529万
 $8,560/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -19570,7 +19570,7 @@
           <t>B | 1042呎 (3房)
 $2210万
 $21,209/呎
-(11年-02月-28日)</t>
+(11年-02月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -19578,7 +19578,7 @@
           <t>C | 841呎 (3房)
 $2034万
 $24,186/呎
-(16年-10月-13日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -19586,7 +19586,7 @@
           <t>D | 840呎 (2房)
 $690万
 $8,211/呎
-(02年-02月-18日)</t>
+(02年-02月)</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
           <t>A | 618呎 (2房)
 $520万
 $8,414/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -19609,7 +19609,7 @@
           <t>B | 1056呎 (3房)
 $2158万
 $20,438/呎
-(11年-03月-21日)</t>
+(11年-03月)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -19617,7 +19617,7 @@
           <t>C | 841呎 (3房)
 $2040万
 $24,257/呎
-(16年-06月-13日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -19625,7 +19625,7 @@
           <t>D | 840呎 (2房)
 $730万
 $8,692/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -19640,7 +19640,7 @@
           <t>A | 618呎 (2房)
 $433万
 $7,010/呎
-(02年-01月-07日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -19648,7 +19648,7 @@
           <t>B | 1042呎 (3房)
 $52262万
 $501,556/呎
-(04年-11月-11日)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -19656,7 +19656,7 @@
           <t>C | 841呎 (3房)
 $4719万
 $56,108/呎
-(15年-12月-23日)</t>
+(15年-12月)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -19664,7 +19664,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,883/呎
-(01年-12月-30日)</t>
+(01年-12月)</t>
         </is>
       </c>
     </row>
@@ -19680,7 +19680,7 @@
           <t>B | 1042呎 (3房)
 $2561万
 $24,579/呎
-(15年-11月-19日)</t>
+(15年-11月)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -19688,7 +19688,7 @@
           <t>C | 841呎 (3房)
 $1911万
 $22,717/呎
-(15年-11月-17日)</t>
+(15年-11月)</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr"/>
@@ -19835,7 +19835,7 @@
           <t>B | 1995呎 (3房)
 $4300万
 $21,554/呎
-(07年-06月-28日)</t>
+(07年-06月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -19843,7 +19843,7 @@
           <t>C | 1366呎 (3房)
 $2963万
 $21,690/呎
-(06年-08月-16日)</t>
+(06年-08月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -19851,7 +19851,7 @@
           <t>D | 1366呎 (3房)
 $3330万
 $24,378/呎
-(07年-08月-23日)</t>
+(07年-08月)</t>
         </is>
       </c>
     </row>
@@ -19866,7 +19866,7 @@
           <t>A | 2181呎 (3房)
 $7618万
 $34,928/呎
-(16年-07月-13日)</t>
+(16年-07月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -19882,7 +19882,7 @@
           <t>C | 1412呎 (3房)
 $2980万
 $21,105/呎
-(07年-08月-22日)</t>
+(07年-08月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -19890,7 +19890,7 @@
           <t>D | 1412呎 (3房)
 $6110万
 $43,275/呎
-(15年-09月-10日)</t>
+(15年-09月)</t>
         </is>
       </c>
     </row>
@@ -19905,7 +19905,7 @@
           <t>A | 1070呎 (3房)
 $2900万
 $27,103/呎
-(11年-03月-20日)</t>
+(11年-03月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -19913,7 +19913,7 @@
           <t>B | 1052呎 (3房)
 $3442万
 $32,721/呎
-(16年-01月-06日)</t>
+(16年-01月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -19921,7 +19921,7 @@
           <t>C | 855呎 (3房)
 $2798万
 $32,722/呎
-(15年-12月-27日)</t>
+(15年-12月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -19929,7 +19929,7 @@
           <t>D | 855呎 (3房)
 $2410万
 $28,187/呎
-(11年-05月-18日)</t>
+(11年-05月)</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
           <t>B | 1052呎 (3房)
 $3300万
 $31,369/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>C | 855呎 (3房)
 $2590万
 $30,292/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -19983,7 +19983,7 @@
           <t>A | 1070呎 (3房)
 $1363万
 $12,738/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -20022,7 +20022,7 @@
           <t>A | 1070呎 (3房)
 $3860万
 $36,075/呎
-(17年-07月-30日)</t>
+(17年-07月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -20030,7 +20030,7 @@
           <t>B | 1052呎 (3房)
 $2789万
 $26,510/呎
-(11年-06月-27日)</t>
+(11年-06月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -20038,7 +20038,7 @@
           <t>C | 855呎 (3房)
 $2511万
 $29,371/呎
-(11年-06月-27日)</t>
+(11年-06月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -20046,7 +20046,7 @@
           <t>D | 855呎 (3房)
 $2850万
 $33,333/呎
-(17年-07月-31日)</t>
+(17年-07月)</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
           <t>A | 1070呎 (3房)
 $2925万
 $27,336/呎
-(11年-06月-14日)</t>
+(11年-06月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -20069,7 +20069,7 @@
           <t>B | 1052呎 (3房)
 $2663万
 $25,312/呎
-(11年-04月-12日)</t>
+(11年-04月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -20077,7 +20077,7 @@
           <t>C | 855呎 (3房)
 $2700万
 $31,579/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -20085,7 +20085,7 @@
           <t>D | 855呎 (3房)
 $2630万
 $30,760/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
           <t>A | 1070呎 (3房)
 $2650万
 $24,766/呎
-(10年-12月-30日)</t>
+(10年-12月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -20108,7 +20108,7 @@
           <t>B | 1052呎 (3房)
 $2580万
 $24,525/呎
-(11年-01月-18日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -20116,7 +20116,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-12月-01日)</t>
+(15年-12月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -20124,7 +20124,7 @@
           <t>D | 855呎 (3房)
 $2619万
 $30,628/呎
-(15年-11月-11日)</t>
+(15年-11月)</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
           <t>A | 1083呎 (3房)
 $1288万
 $11,893/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -20147,7 +20147,7 @@
           <t>B | 1052呎 (3房)
 $2520万
 $23,954/呎
-(11年-01月-12日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -20155,7 +20155,7 @@
           <t>C | 855呎 (3房)
 $4719万
 $55,189/呎
-(15年-12月-23日)</t>
+(15年-12月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -20163,7 +20163,7 @@
           <t>D | 855呎 (3房)
 $2602万
 $30,436/呎
-(15年-11月-08日)</t>
+(15年-11月)</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20178,7 @@
           <t>A | 1070呎 (3房)
 $2715万
 $25,374/呎
-(11年-01月-23日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -20186,7 +20186,7 @@
           <t>B | 1052呎 (3房)
 $3372万
 $32,055/呎
-(16年-06月-21日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -20194,7 +20194,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-09月-29日)</t>
+(15年-09月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -20202,7 +20202,7 @@
           <t>D | 855呎 (3房)
 $2265万
 $26,491/呎
-(11年-01月-23日)</t>
+(11年-01月)</t>
         </is>
       </c>
     </row>
@@ -20241,7 +20241,7 @@
           <t>D | 855呎 (3房)
 $988万
 $11,557/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
           <t>A | 1052呎 (3房)
 $3376万
 $32,095/呎
-(16年-06月-13日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -20264,7 +20264,7 @@
           <t>B | 1032呎 (3房)
 $2448万
 $23,721/呎
-(11年-05月-29日)</t>
+(11年-05月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -20272,7 +20272,7 @@
           <t>C | 841呎 (3房)
 $1792万
 $21,307/呎
-(08年-03月-26日)</t>
+(08年-03月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -20280,7 +20280,7 @@
           <t>D | 841呎 (3房)
 $2560万
 $30,440/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -20295,7 +20295,7 @@
           <t>A | 1052呎 (3房)
 $1192万
 $11,335/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -20303,7 +20303,7 @@
           <t>B | 1032呎 (3房)
 $2250万
 $21,802/呎
-(11年-01月-16日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -20311,7 +20311,7 @@
           <t>C | 841呎 (3房)
 $2080万
 $24,732/呎
-(11年-01月-26日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -20319,7 +20319,7 @@
           <t>D | 841呎 (3房)
 $2154万
 $25,612/呎
-(11年-06月-01日)</t>
+(11年-06月)</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
           <t>A | 1065呎 (3房)
 $2350万
 $22,066/呎
-(11年-01月-23日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -20342,7 +20342,7 @@
           <t>B | 1032呎 (3房)
 $2210万
 $21,415/呎
-(11年-01月-16日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -20358,7 +20358,7 @@
           <t>D | 865呎 (3房)
 $920万
 $10,631/呎
-(02年-04月-19日)</t>
+(02年-04月)</t>
         </is>
       </c>
     </row>
@@ -20373,7 +20373,7 @@
           <t>A | 1052呎 (3房)
 $1167万
 $11,093/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -20381,7 +20381,7 @@
           <t>B | 1032呎 (3房)
 $2160万
 $20,930/呎
-(11年-01月-18日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -20389,7 +20389,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,768/呎
-(11年-03月-08日)</t>
+(11年-03月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -20397,7 +20397,7 @@
           <t>D | 841呎 (3房)
 $2118万
 $25,184/呎
-(11年-06月-13日)</t>
+(11年-06月)</t>
         </is>
       </c>
     </row>
@@ -20412,7 +20412,7 @@
           <t>A | 1052呎 (3房)
 $1210万
 $11,507/呎
-(02年-01月-16日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -20420,7 +20420,7 @@
           <t>B | 1038呎 (3房)
 $2160万
 $20,809/呎
-(11年-01月-06日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -20428,7 +20428,7 @@
           <t>C | 840呎 (2房)
 $1960万
 $23,333/呎
-(11年-01月-18日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -20436,7 +20436,7 @@
           <t>D | 841呎 (3房)
 $2380万
 $28,299/呎
-(15年-11月-05日)</t>
+(15年-11月)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
           <t>A | 1052呎 (3房)
 $1197万
 $11,378/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -20467,7 +20467,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月-23日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -20475,7 +20475,7 @@
           <t>D | 841呎 (3房)
 $2000万
 $23,781/呎
-(11年-03月-16日)</t>
+(11年-03月)</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
           <t>A | 1064呎 (3房)
 $1125万
 $10,573/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -20498,7 +20498,7 @@
           <t>B | 1032呎 (3房)
 $2100万
 $20,349/呎
-(11年-01月-17日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -20506,7 +20506,7 @@
           <t>C | 840呎 (2房)
 $1900万
 $22,619/呎
-(11年-01月-13日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,253/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
           <t>A | 1052呎 (3房)
 $1140万
 $10,833/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -20537,7 +20537,7 @@
           <t>B | 1038呎 (3房)
 $2140万
 $20,617/呎
-(11年-01月-16日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -20545,7 +20545,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月-30日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -20553,7 +20553,7 @@
           <t>D | 841呎 (3房)
 $2363万
 $28,103/呎
-(15年-11月-12日)</t>
+(15年-11月)</t>
         </is>
       </c>
     </row>
@@ -20568,7 +20568,7 @@
           <t>A | 1052呎 (3房)
 $1015万
 $9,651/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -20576,7 +20576,7 @@
           <t>B | 1032呎 (3房)
 $953万
 $9,232/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -20592,7 +20592,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,249/呎
-(02年-01月-09日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
           <t>A | 1052呎 (3房)
 $1064万
 $10,113/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -20615,7 +20615,7 @@
           <t>B | 1032呎 (3房)
 $1950万
 $18,895/呎
-(10年-12月-30日)</t>
+(10年-12月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -20631,7 +20631,7 @@
           <t>D | 841呎 (3房)
 $896万
 $10,649/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20646,7 +20646,7 @@
           <t>A | 1064呎 (3房)
 $1061万
 $9,976/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -20654,7 +20654,7 @@
           <t>B | 1032呎 (3房)
 $1938万
 $18,779/呎
-(11年-01月-13日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -20662,7 +20662,7 @@
           <t>C | 863呎 (2房)
 $1810万
 $20,973/呎
-(11年-01月-10日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -20670,7 +20670,7 @@
           <t>D | 841呎 (3房)
 $1838万
 $21,855/呎
-(11年-01月-31日)</t>
+(11年-01月)</t>
         </is>
       </c>
     </row>
@@ -20685,7 +20685,7 @@
           <t>A | 1064呎 (3房)
 $1040万
 $9,773/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -20693,7 +20693,7 @@
           <t>B | 1032呎 (3房)
 $1900万
 $18,411/呎
-(10年-12月-28日)</t>
+(10年-12月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -20701,7 +20701,7 @@
           <t>C | 840呎 (2房)
 $1740万
 $20,714/呎
-(11年-01月-11日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -20709,7 +20709,7 @@
           <t>D | 841呎 (3房)
 $1790万
 $21,284/呎
-(11年-01月-23日)</t>
+(11年-01月)</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
           <t>A | 1065呎 (3房)
 $942万
 $8,848/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -20732,7 +20732,7 @@
           <t>B | 1032呎 (3房)
 $1867万
 $18,094/呎
-(10年-12月-19日)</t>
+(10年-12月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -20740,7 +20740,7 @@
           <t>C | 865呎 (2房)
 $1723万
 $19,916/呎
-(10年-12月-19日)</t>
+(10年-12月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -20748,7 +20748,7 @@
           <t>D | 841呎 (3房)
 $913万
 $10,856/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20763,7 +20763,7 @@
           <t>A | 1042呎 (3房)
 $1065万
 $10,221/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -20771,7 +20771,7 @@
           <t>B | 1032呎 (3房)
 $1918万
 $18,585/呎
-(11年-01月-05日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -20779,7 +20779,7 @@
           <t>C | 840呎 (2房)
 $881万
 $10,492/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -20787,7 +20787,7 @@
           <t>D | 841呎 (3房)
 $733万
 $8,721/呎
-(02年-01月-07日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
           <t>A | 1042呎 (3房)
 $1015万
 $9,740/呎
-(02年-03月-15日)</t>
+(02年-03月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -20810,7 +20810,7 @@
           <t>B | 1039呎 (3房)
 $892万
 $8,586/呎
-(02年-01月-09日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -20818,7 +20818,7 @@
           <t>C | 840呎 (2房)
 $1780万
 $21,190/呎
-(11年-01月-20日)</t>
+(11年-01月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -20841,7 +20841,7 @@
           <t>A | 1056呎 (3房)
 $832万
 $7,877/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -20849,7 +20849,7 @@
           <t>B | 1032呎 (3房)
 $840万
 $8,140/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -20857,7 +20857,7 @@
           <t>C | 840呎 (2房)
 $750万
 $8,935/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -20865,7 +20865,7 @@
           <t>D | 865呎 (3房)
 $769万
 $8,890/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20880,7 +20880,7 @@
           <t>A | 1042呎 (3房)
 $858万
 $8,234/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -20888,7 +20888,7 @@
           <t>B | 618呎 (2房)
 $487万
 $7,880/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -20896,7 +20896,7 @@
           <t>C | 840呎 (2房)
 $791万
 $9,417/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -20904,7 +20904,7 @@
           <t>D | 841呎 (2房)
 $733万
 $8,717/呎
-(02年-01月-09日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
           <t>A | 1042呎 (3房)
 $891万
 $8,548/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -20927,7 +20927,7 @@
           <t>B | 619呎 (2房)
 $486万
 $7,851/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -20935,7 +20935,7 @@
           <t>C | 840呎 (2房)
 $723万
 $8,607/呎
-(02年-01月-07日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -20943,7 +20943,7 @@
           <t>D | 841呎 (2房)
 $715万
 $8,501/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20958,7 +20958,7 @@
           <t>A | 1042呎 (3房)
 $828万
 $7,947/呎
-(01年-12月-27日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -20966,7 +20966,7 @@
           <t>B | 618呎 (2房)
 $481万
 $7,783/呎
-(01年-12月-27日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -20974,7 +20974,7 @@
           <t>C | 840呎 (2房)
 $709万
 $8,445/呎
-(01年-12月-27日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -20982,7 +20982,7 @@
           <t>D | 865呎 (2房)
 $754万
 $8,716/呎
-(02年-01月-09日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
           <t>A | 1042呎 (3房)
 $866万
 $8,311/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -21005,7 +21005,7 @@
           <t>B | 618呎 (2房)
 $426万
 $6,893/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -21013,7 +21013,7 @@
           <t>C | 840呎 (2房)
 $650万
 $7,736/呎
-(02年-01月-08日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -21021,7 +21021,7 @@
           <t>D | 840呎 (2房)
 $1490万
 $17,738/呎
-(11年-01月-16日)</t>
+(11年-01月)</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
           <t>A | 1056呎 (3房)
 $855万
 $8,097/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -21044,7 +21044,7 @@
           <t>B | 618呎 (2房)
 $456万
 $7,385/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -21052,7 +21052,7 @@
           <t>C | 840呎 (2房)
 $724万
 $8,625/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -21060,7 +21060,7 @@
           <t>D | 840呎 (2房)
 $718万
 $8,548/呎
-(02年-01月-01日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>
@@ -21075,7 +21075,7 @@
           <t>A | 1042呎 (3房)
 $760万
 $7,295/呎
-(02年-01月-09日)</t>
+(02年-01月)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -21083,7 +21083,7 @@
           <t>B | 618呎 (2房)
 $373万
 $6,042/呎
-(01年-12月-30日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -21091,7 +21091,7 @@
           <t>C | 840呎 (2房)
 $707万
 $8,417/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -21099,7 +21099,7 @@
           <t>D | 840呎 (2房)
 $667万
 $7,936/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
           <t>A | 1042呎 (3房)
 $732万
 $7,022/呎
-(01年-12月-28日)</t>
+(01年-12月)</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr"/>
@@ -21124,7 +21124,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,875/呎
-(02年-01月-09日)</t>
+(02年-01月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -18431,7 +18431,7 @@
           <t>A | 2059呎 (3房)
 $8888万
 $43,167/呎
-(16年-09月)</t>
+(16年-09月-01日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -18439,7 +18439,7 @@
           <t>B | 2093呎 (3房)
 $10528万
 $50,301/呎
-(17年-01月)</t>
+(17年-01月-12日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -18455,7 +18455,7 @@
           <t>D | 1709呎 (3房)
 $6300万
 $36,864/呎
-(16年-09月)</t>
+(16年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
           <t>A | 1058呎 (3房)
 $52262万
 $493,971/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -18478,7 +18478,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -18486,7 +18486,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -18494,7 +18494,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -18509,7 +18509,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -18517,7 +18517,7 @@
           <t>B | 1083呎 (3房)
 $52262万
 $482,568/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -18525,7 +18525,7 @@
           <t>C | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -18533,7 +18533,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -18572,7 +18572,7 @@
           <t>D | 855呎 (3房)
 $2550万
 $29,825/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
     </row>
@@ -18587,7 +18587,7 @@
           <t>A | 1052呎 (3房)
 $3467万
 $32,956/呎
-(16年-07月)</t>
+(16年-07月-11日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -18595,7 +18595,7 @@
           <t>B | 1070呎 (3房)
 $3130万
 $29,252/呎
-(11年-02月)</t>
+(11年-02月-20日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -18603,7 +18603,7 @@
           <t>C | 855呎 (3房)
 $2866万
 $33,518/呎
-(15年-10月)</t>
+(15年-10月-18日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -18611,7 +18611,7 @@
           <t>D | 855呎 (3房)
 $2643万
 $30,917/呎
-(15年-11月)</t>
+(15年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -18634,7 +18634,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -18642,7 +18642,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -18650,7 +18650,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -18673,7 +18673,7 @@
           <t>B | 1070呎 (3房)
 $3250万
 $30,374/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -18681,7 +18681,7 @@
           <t>C | 855呎 (3房)
 $2830万
 $33,099/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -18689,7 +18689,7 @@
           <t>D | 855呎 (3房)
 $2620万
 $30,643/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -18704,7 +18704,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -18712,7 +18712,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -18720,7 +18720,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -18728,7 +18728,7 @@
           <t>D | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
           <t>A | 1052呎 (3房)
 $3426万
 $32,564/呎
-(16年-10月)</t>
+(16年-10月-06日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -18751,7 +18751,7 @@
           <t>B | 1083呎 (3房)
 $2950万
 $27,239/呎
-(11年-01月)</t>
+(11年-01月-09日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -18759,7 +18759,7 @@
           <t>C | 855呎 (3房)
 $2833万
 $33,133/呎
-(16年-06月)</t>
+(16年-06月-13日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -18767,7 +18767,7 @@
           <t>D | 855呎 (3房)
 $2640万
 $30,871/呎
-(16年-10月)</t>
+(16年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
           <t>A | 1052呎 (3房)
 $3100万
 $29,468/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -18790,7 +18790,7 @@
           <t>B | 1070呎 (3房)
 $3418万
 $31,944/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -18806,7 +18806,7 @@
           <t>D | 855呎 (3房)
 $2430万
 $28,421/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -18821,7 +18821,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -18829,7 +18829,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -18837,7 +18837,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -18845,7 +18845,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18860,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -18868,7 +18868,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -18876,7 +18876,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -18884,7 +18884,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -18899,7 +18899,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -18907,7 +18907,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -18915,7 +18915,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -18923,7 +18923,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
           <t>B | 1052呎 (3房)
 $1269万
 $12,064/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -18977,7 +18977,7 @@
           <t>A | 1032呎 (3房)
 $3030万
 $29,360/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -18985,7 +18985,7 @@
           <t>B | 1052呎 (3房)
 $1255万
 $11,931/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -18993,7 +18993,7 @@
           <t>C | 841呎 (3房)
 $2550万
 $30,321/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -19024,7 +19024,7 @@
           <t>B | 1052呎 (3房)
 $1305万
 $12,405/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -19040,7 +19040,7 @@
           <t>D | 840呎 (2房)
 $1008万
 $11,994/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
           <t>B | 1052呎 (3房)
 $2750万
 $26,141/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -19071,7 +19071,7 @@
           <t>C | 865呎 (3房)
 $2370万
 $27,399/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -19094,7 +19094,7 @@
           <t>A | 1032呎 (3房)
 $2280万
 $22,093/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -19102,7 +19102,7 @@
           <t>B | 1065呎 (3房)
 $2553万
 $23,972/呎
-(11年-01月)</t>
+(11年-01月-11日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -19110,7 +19110,7 @@
           <t>C | 841呎 (3房)
 $2578万
 $30,649/呎
-(15年-10月)</t>
+(15年-10月-04日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -19118,7 +19118,7 @@
           <t>D | 840呎 (2房)
 $2339万
 $27,842/呎
-(16年-06月)</t>
+(16年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -19133,7 +19133,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -19141,7 +19141,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -19149,7 +19149,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -19157,7 +19157,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -19180,7 +19180,7 @@
           <t>B | 1052呎 (3房)
 $2800万
 $26,616/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -19188,7 +19188,7 @@
           <t>C | 841呎 (3房)
 $2350万
 $27,943/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -19196,7 +19196,7 @@
           <t>D | 840呎 (2房)
 $889万
 $10,585/呎
-(02年-01月)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -19211,7 +19211,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -19219,7 +19219,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -19227,7 +19227,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -19235,7 +19235,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -19258,7 +19258,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -19266,7 +19266,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -19274,7 +19274,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -19289,7 +19289,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -19297,7 +19297,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -19305,7 +19305,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -19313,7 +19313,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -19328,7 +19328,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -19352,7 +19352,7 @@
           <t>D | 840呎 (2房)
 $894万
 $10,637/呎
-(02年-02月)</t>
+(02年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -19367,7 +19367,7 @@
           <t>A | 1032呎 (3房)
 $998万
 $9,671/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -19375,7 +19375,7 @@
           <t>B | 1042呎 (3房)
 $2680万
 $25,720/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -19383,7 +19383,7 @@
           <t>C | 841呎 (3房)
 $2370万
 $28,181/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -19391,7 +19391,7 @@
           <t>D | 840呎 (2房)
 $843万
 $10,032/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -19414,7 +19414,7 @@
           <t>B | 1056呎 (3房)
 $52262万
 $494,906/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -19422,7 +19422,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -19430,7 +19430,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -19445,7 +19445,7 @@
           <t>A | 620呎 (2房)
 $550万
 $8,863/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -19453,7 +19453,7 @@
           <t>B | 1042呎 (3房)
 $2088万
 $20,038/呎
-(11年-01月)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -19461,7 +19461,7 @@
           <t>C | 841呎 (3房)
 $1960万
 $23,306/呎
-(11年-06月)</t>
+(11年-06月-16日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -19469,7 +19469,7 @@
           <t>D | 840呎 (2房)
 $760万
 $9,048/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
           <t>A | 618呎 (2房)
 $465万
 $7,518/呎
-(01年-12月)</t>
+(01年-12月-30日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -19492,7 +19492,7 @@
           <t>B | 1042呎 (3房)
 $1049万
 $10,067/呎
-(02年-03月)</t>
+(02年-03月-25日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -19500,7 +19500,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,774/呎
-(15年-09月)</t>
+(15年-09月-28日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -19508,7 +19508,7 @@
           <t>D | 840呎 (2房)
 $1670万
 $19,881/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -19523,7 +19523,7 @@
           <t>A | 618呎 (2房)
 $482万
 $7,799/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -19531,7 +19531,7 @@
           <t>B | 1042呎 (3房)
 $2188万
 $20,998/呎
-(11年-01月)</t>
+(11年-01月-20日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -19539,7 +19539,7 @@
           <t>C | 841呎 (3房)
 $881万
 $10,476/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -19547,7 +19547,7 @@
           <t>D | 840呎 (2房)
 $785万
 $9,345/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19562,7 @@
           <t>A | 618呎 (2房)
 $529万
 $8,560/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -19570,7 +19570,7 @@
           <t>B | 1042呎 (3房)
 $2210万
 $21,209/呎
-(11年-02月)</t>
+(11年-02月-28日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -19578,7 +19578,7 @@
           <t>C | 841呎 (3房)
 $2034万
 $24,186/呎
-(16年-10月)</t>
+(16年-10月-13日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -19586,7 +19586,7 @@
           <t>D | 840呎 (2房)
 $690万
 $8,211/呎
-(02年-02月)</t>
+(02年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
           <t>A | 618呎 (2房)
 $520万
 $8,414/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -19609,7 +19609,7 @@
           <t>B | 1056呎 (3房)
 $2158万
 $20,438/呎
-(11年-03月)</t>
+(11年-03月-21日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -19617,7 +19617,7 @@
           <t>C | 841呎 (3房)
 $2040万
 $24,257/呎
-(16年-06月)</t>
+(16年-06月-13日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -19625,7 +19625,7 @@
           <t>D | 840呎 (2房)
 $730万
 $8,692/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -19640,7 +19640,7 @@
           <t>A | 618呎 (2房)
 $433万
 $7,010/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -19648,7 +19648,7 @@
           <t>B | 1042呎 (3房)
 $52262万
 $501,556/呎
-(04年-11月)</t>
+(04年-11月-11日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -19656,7 +19656,7 @@
           <t>C | 841呎 (3房)
 $4719万
 $56,108/呎
-(15年-12月)</t>
+(15年-12月-23日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -19664,7 +19664,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,883/呎
-(01年-12月)</t>
+(01年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -19680,7 +19680,7 @@
           <t>B | 1042呎 (3房)
 $2561万
 $24,579/呎
-(15年-11月)</t>
+(15年-11月-19日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -19688,7 +19688,7 @@
           <t>C | 841呎 (3房)
 $1911万
 $22,717/呎
-(15年-11月)</t>
+(15年-11月-17日)</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr"/>
@@ -19835,7 +19835,7 @@
           <t>B | 1995呎 (3房)
 $4300万
 $21,554/呎
-(07年-06月)</t>
+(07年-06月-28日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -19843,7 +19843,7 @@
           <t>C | 1366呎 (3房)
 $2963万
 $21,690/呎
-(06年-08月)</t>
+(06年-08月-16日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -19851,7 +19851,7 @@
           <t>D | 1366呎 (3房)
 $3330万
 $24,378/呎
-(07年-08月)</t>
+(07年-08月-23日)</t>
         </is>
       </c>
     </row>
@@ -19866,7 +19866,7 @@
           <t>A | 2181呎 (3房)
 $7618万
 $34,928/呎
-(16年-07月)</t>
+(16年-07月-13日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -19882,7 +19882,7 @@
           <t>C | 1412呎 (3房)
 $2980万
 $21,105/呎
-(07年-08月)</t>
+(07年-08月-22日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -19890,7 +19890,7 @@
           <t>D | 1412呎 (3房)
 $6110万
 $43,275/呎
-(15年-09月)</t>
+(15年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -19905,7 +19905,7 @@
           <t>A | 1070呎 (3房)
 $2900万
 $27,103/呎
-(11年-03月)</t>
+(11年-03月-20日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -19913,7 +19913,7 @@
           <t>B | 1052呎 (3房)
 $3442万
 $32,721/呎
-(16年-01月)</t>
+(16年-01月-06日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -19921,7 +19921,7 @@
           <t>C | 855呎 (3房)
 $2798万
 $32,722/呎
-(15年-12月)</t>
+(15年-12月-27日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -19929,7 +19929,7 @@
           <t>D | 855呎 (3房)
 $2410万
 $28,187/呎
-(11年-05月)</t>
+(11年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
           <t>B | 1052呎 (3房)
 $3300万
 $31,369/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>C | 855呎 (3房)
 $2590万
 $30,292/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -19983,7 +19983,7 @@
           <t>A | 1070呎 (3房)
 $1363万
 $12,738/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -20022,7 +20022,7 @@
           <t>A | 1070呎 (3房)
 $3860万
 $36,075/呎
-(17年-07月)</t>
+(17年-07月-30日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -20030,7 +20030,7 @@
           <t>B | 1052呎 (3房)
 $2789万
 $26,510/呎
-(11年-06月)</t>
+(11年-06月-27日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -20038,7 +20038,7 @@
           <t>C | 855呎 (3房)
 $2511万
 $29,371/呎
-(11年-06月)</t>
+(11年-06月-27日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -20046,7 +20046,7 @@
           <t>D | 855呎 (3房)
 $2850万
 $33,333/呎
-(17年-07月)</t>
+(17年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
           <t>A | 1070呎 (3房)
 $2925万
 $27,336/呎
-(11年-06月)</t>
+(11年-06月-14日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -20069,7 +20069,7 @@
           <t>B | 1052呎 (3房)
 $2663万
 $25,312/呎
-(11年-04月)</t>
+(11年-04月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -20077,7 +20077,7 @@
           <t>C | 855呎 (3房)
 $2700万
 $31,579/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -20085,7 +20085,7 @@
           <t>D | 855呎 (3房)
 $2630万
 $30,760/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
           <t>A | 1070呎 (3房)
 $2650万
 $24,766/呎
-(10年-12月)</t>
+(10年-12月-30日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -20108,7 +20108,7 @@
           <t>B | 1052呎 (3房)
 $2580万
 $24,525/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -20116,7 +20116,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-12月)</t>
+(15年-12月-01日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -20124,7 +20124,7 @@
           <t>D | 855呎 (3房)
 $2619万
 $30,628/呎
-(15年-11月)</t>
+(15年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
           <t>A | 1083呎 (3房)
 $1288万
 $11,893/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -20147,7 +20147,7 @@
           <t>B | 1052呎 (3房)
 $2520万
 $23,954/呎
-(11年-01月)</t>
+(11年-01月-12日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -20155,7 +20155,7 @@
           <t>C | 855呎 (3房)
 $4719万
 $55,189/呎
-(15年-12月)</t>
+(15年-12月-23日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -20163,7 +20163,7 @@
           <t>D | 855呎 (3房)
 $2602万
 $30,436/呎
-(15年-11月)</t>
+(15年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20178,7 @@
           <t>A | 1070呎 (3房)
 $2715万
 $25,374/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -20186,7 +20186,7 @@
           <t>B | 1052呎 (3房)
 $3372万
 $32,055/呎
-(16年-06月)</t>
+(16年-06月-21日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -20194,7 +20194,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-09月)</t>
+(15年-09月-29日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -20202,7 +20202,7 @@
           <t>D | 855呎 (3房)
 $2265万
 $26,491/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -20241,7 +20241,7 @@
           <t>D | 855呎 (3房)
 $988万
 $11,557/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
           <t>A | 1052呎 (3房)
 $3376万
 $32,095/呎
-(16年-06月)</t>
+(16年-06月-13日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -20264,7 +20264,7 @@
           <t>B | 1032呎 (3房)
 $2448万
 $23,721/呎
-(11年-05月)</t>
+(11年-05月-29日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -20272,7 +20272,7 @@
           <t>C | 841呎 (3房)
 $1792万
 $21,307/呎
-(08年-03月)</t>
+(08年-03月-26日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -20280,7 +20280,7 @@
           <t>D | 841呎 (3房)
 $2560万
 $30,440/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -20295,7 +20295,7 @@
           <t>A | 1052呎 (3房)
 $1192万
 $11,335/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -20303,7 +20303,7 @@
           <t>B | 1032呎 (3房)
 $2250万
 $21,802/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -20311,7 +20311,7 @@
           <t>C | 841呎 (3房)
 $2080万
 $24,732/呎
-(11年-01月)</t>
+(11年-01月-26日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -20319,7 +20319,7 @@
           <t>D | 841呎 (3房)
 $2154万
 $25,612/呎
-(11年-06月)</t>
+(11年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
           <t>A | 1065呎 (3房)
 $2350万
 $22,066/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -20342,7 +20342,7 @@
           <t>B | 1032呎 (3房)
 $2210万
 $21,415/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -20358,7 +20358,7 @@
           <t>D | 865呎 (3房)
 $920万
 $10,631/呎
-(02年-04月)</t>
+(02年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -20373,7 +20373,7 @@
           <t>A | 1052呎 (3房)
 $1167万
 $11,093/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -20381,7 +20381,7 @@
           <t>B | 1032呎 (3房)
 $2160万
 $20,930/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -20389,7 +20389,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,768/呎
-(11年-03月)</t>
+(11年-03月-08日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -20397,7 +20397,7 @@
           <t>D | 841呎 (3房)
 $2118万
 $25,184/呎
-(11年-06月)</t>
+(11年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -20412,7 +20412,7 @@
           <t>A | 1052呎 (3房)
 $1210万
 $11,507/呎
-(02年-01月)</t>
+(02年-01月-16日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -20420,7 +20420,7 @@
           <t>B | 1038呎 (3房)
 $2160万
 $20,809/呎
-(11年-01月)</t>
+(11年-01月-06日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -20428,7 +20428,7 @@
           <t>C | 840呎 (2房)
 $1960万
 $23,333/呎
-(11年-01月)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -20436,7 +20436,7 @@
           <t>D | 841呎 (3房)
 $2380万
 $28,299/呎
-(15年-11月)</t>
+(15年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
           <t>A | 1052呎 (3房)
 $1197万
 $11,378/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -20467,7 +20467,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -20475,7 +20475,7 @@
           <t>D | 841呎 (3房)
 $2000万
 $23,781/呎
-(11年-03月)</t>
+(11年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
           <t>A | 1064呎 (3房)
 $1125万
 $10,573/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -20498,7 +20498,7 @@
           <t>B | 1032呎 (3房)
 $2100万
 $20,349/呎
-(11年-01月)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -20506,7 +20506,7 @@
           <t>C | 840呎 (2房)
 $1900万
 $22,619/呎
-(11年-01月)</t>
+(11年-01月-13日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,253/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
           <t>A | 1052呎 (3房)
 $1140万
 $10,833/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -20537,7 +20537,7 @@
           <t>B | 1038呎 (3房)
 $2140万
 $20,617/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -20545,7 +20545,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月)</t>
+(11年-01月-30日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -20553,7 +20553,7 @@
           <t>D | 841呎 (3房)
 $2363万
 $28,103/呎
-(15年-11月)</t>
+(15年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -20568,7 +20568,7 @@
           <t>A | 1052呎 (3房)
 $1015万
 $9,651/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -20576,7 +20576,7 @@
           <t>B | 1032呎 (3房)
 $953万
 $9,232/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -20592,7 +20592,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,249/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
           <t>A | 1052呎 (3房)
 $1064万
 $10,113/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -20615,7 +20615,7 @@
           <t>B | 1032呎 (3房)
 $1950万
 $18,895/呎
-(10年-12月)</t>
+(10年-12月-30日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -20631,7 +20631,7 @@
           <t>D | 841呎 (3房)
 $896万
 $10,649/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -20646,7 +20646,7 @@
           <t>A | 1064呎 (3房)
 $1061万
 $9,976/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -20654,7 +20654,7 @@
           <t>B | 1032呎 (3房)
 $1938万
 $18,779/呎
-(11年-01月)</t>
+(11年-01月-13日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -20662,7 +20662,7 @@
           <t>C | 863呎 (2房)
 $1810万
 $20,973/呎
-(11年-01月)</t>
+(11年-01月-10日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -20670,7 +20670,7 @@
           <t>D | 841呎 (3房)
 $1838万
 $21,855/呎
-(11年-01月)</t>
+(11年-01月-31日)</t>
         </is>
       </c>
     </row>
@@ -20685,7 +20685,7 @@
           <t>A | 1064呎 (3房)
 $1040万
 $9,773/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -20693,7 +20693,7 @@
           <t>B | 1032呎 (3房)
 $1900万
 $18,411/呎
-(10年-12月)</t>
+(10年-12月-28日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -20701,7 +20701,7 @@
           <t>C | 840呎 (2房)
 $1740万
 $20,714/呎
-(11年-01月)</t>
+(11年-01月-11日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -20709,7 +20709,7 @@
           <t>D | 841呎 (3房)
 $1790万
 $21,284/呎
-(11年-01月)</t>
+(11年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
           <t>A | 1065呎 (3房)
 $942万
 $8,848/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -20732,7 +20732,7 @@
           <t>B | 1032呎 (3房)
 $1867万
 $18,094/呎
-(10年-12月)</t>
+(10年-12月-19日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -20740,7 +20740,7 @@
           <t>C | 865呎 (2房)
 $1723万
 $19,916/呎
-(10年-12月)</t>
+(10年-12月-19日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -20748,7 +20748,7 @@
           <t>D | 841呎 (3房)
 $913万
 $10,856/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -20763,7 +20763,7 @@
           <t>A | 1042呎 (3房)
 $1065万
 $10,221/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -20771,7 +20771,7 @@
           <t>B | 1032呎 (3房)
 $1918万
 $18,585/呎
-(11年-01月)</t>
+(11年-01月-05日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -20779,7 +20779,7 @@
           <t>C | 840呎 (2房)
 $881万
 $10,492/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -20787,7 +20787,7 @@
           <t>D | 841呎 (3房)
 $733万
 $8,721/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
           <t>A | 1042呎 (3房)
 $1015万
 $9,740/呎
-(02年-03月)</t>
+(02年-03月-15日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -20810,7 +20810,7 @@
           <t>B | 1039呎 (3房)
 $892万
 $8,586/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -20818,7 +20818,7 @@
           <t>C | 840呎 (2房)
 $1780万
 $21,190/呎
-(11年-01月)</t>
+(11年-01月-20日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -20841,7 +20841,7 @@
           <t>A | 1056呎 (3房)
 $832万
 $7,877/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -20849,7 +20849,7 @@
           <t>B | 1032呎 (3房)
 $840万
 $8,140/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -20857,7 +20857,7 @@
           <t>C | 840呎 (2房)
 $750万
 $8,935/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -20865,7 +20865,7 @@
           <t>D | 865呎 (3房)
 $769万
 $8,890/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -20880,7 +20880,7 @@
           <t>A | 1042呎 (3房)
 $858万
 $8,234/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -20888,7 +20888,7 @@
           <t>B | 618呎 (2房)
 $487万
 $7,880/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -20896,7 +20896,7 @@
           <t>C | 840呎 (2房)
 $791万
 $9,417/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -20904,7 +20904,7 @@
           <t>D | 841呎 (2房)
 $733万
 $8,717/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
           <t>A | 1042呎 (3房)
 $891万
 $8,548/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -20927,7 +20927,7 @@
           <t>B | 619呎 (2房)
 $486万
 $7,851/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -20935,7 +20935,7 @@
           <t>C | 840呎 (2房)
 $723万
 $8,607/呎
-(02年-01月)</t>
+(02年-01月-07日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -20943,7 +20943,7 @@
           <t>D | 841呎 (2房)
 $715万
 $8,501/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -20958,7 +20958,7 @@
           <t>A | 1042呎 (3房)
 $828万
 $7,947/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -20966,7 +20966,7 @@
           <t>B | 618呎 (2房)
 $481万
 $7,783/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -20974,7 +20974,7 @@
           <t>C | 840呎 (2房)
 $709万
 $8,445/呎
-(01年-12月)</t>
+(01年-12月-27日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -20982,7 +20982,7 @@
           <t>D | 865呎 (2房)
 $754万
 $8,716/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
           <t>A | 1042呎 (3房)
 $866万
 $8,311/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -21005,7 +21005,7 @@
           <t>B | 618呎 (2房)
 $426万
 $6,893/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -21013,7 +21013,7 @@
           <t>C | 840呎 (2房)
 $650万
 $7,736/呎
-(02年-01月)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -21021,7 +21021,7 @@
           <t>D | 840呎 (2房)
 $1490万
 $17,738/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
           <t>A | 1056呎 (3房)
 $855万
 $8,097/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -21044,7 +21044,7 @@
           <t>B | 618呎 (2房)
 $456万
 $7,385/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -21052,7 +21052,7 @@
           <t>C | 840呎 (2房)
 $724万
 $8,625/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -21060,7 +21060,7 @@
           <t>D | 840呎 (2房)
 $718万
 $8,548/呎
-(02年-01月)</t>
+(02年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -21075,7 +21075,7 @@
           <t>A | 1042呎 (3房)
 $760万
 $7,295/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -21083,7 +21083,7 @@
           <t>B | 618呎 (2房)
 $373万
 $6,042/呎
-(01年-12月)</t>
+(01年-12月-30日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -21091,7 +21091,7 @@
           <t>C | 840呎 (2房)
 $707万
 $8,417/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -21099,7 +21099,7 @@
           <t>D | 840呎 (2房)
 $667万
 $7,936/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
           <t>A | 1042呎 (3房)
 $732万
 $7,022/呎
-(01年-12月)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr"/>
@@ -21124,7 +21124,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,875/呎
-(02年-01月)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-罗便臣道80号.xlsx
+++ b/files/港岛-半山区西部-罗便臣道80号.xlsx
@@ -127,7 +127,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -272,7 +273,7 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1699,7 +1700,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -18369,12 +18370,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -18556,7 +18557,7 @@
           <t>B | 1083呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
